--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -2345,7 +2345,7 @@
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>PREENCHER com os vales adiantados durante setembro.</t>
+          <t xml:space="preserve">PREENCHER com os vales adiantados durante setembro. </t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>PREENCHER com as passagens compradas para outubro/2026.</t>
+          <t xml:space="preserve">PREENCHER com as passagens compradas. </t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -800,7 +800,7 @@
       <c r="A20" s="4" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>DSR de setembro/2026: 4 domingos + o feriado de 07/09 ÷ 25 dias úteis = fator 0,200000</t>
+          <t>DSR de setembro/2026: 4 domingos + os feriados de 07/09 e 08/09 (municipal) = 6 ÷ 24 dias úteis = fator 0,250000</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Domingos: 06, 13, 20 e 27/09/2026, mais o feriado de 07/09 (segunda-feira). CONFERIR feriados municipais.</t>
+          <t>Domingos: 06, 13, 20 e 27/09/2026, mais os feriados de 07/09 (Independência, segunda) e 08/09 (municipal, terça).</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</t>
+          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -10,17 +10,19 @@
     <sheet name="CAPA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PARÂMETROS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BASE INOVAFARMA SET.26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HOLERITE SET.26" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LISTA CONTABILIDADE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GANHOS DO COLABORADOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PONTO SET.26" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="METAS SET.26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HOLERITE SET.26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GANHOS DO COLABORADOR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PONTO SET.26" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$H$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'METAS SET.26'!$A$11:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,11 +30,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +89,23 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -168,12 +188,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -208,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,11 +237,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,39 +276,61 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -654,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -886,7 +928,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Prêmios do programa de metas: lançar na aba METAS SET.26 a venda realizada, os dias trabalhados, o pré-vencido vendido, a Meta 2 e a perfumaria da loja.</t>
         </is>
       </c>
     </row>
@@ -1015,6 +1057,14 @@
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="4" t="inlineStr"/>
       <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>METAS SET.26 — programa de metas de setembro (4 metas), com o prêmio de cada um calculado e ligado ao holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
@@ -1730,7 +1780,656 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:T26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE METAS E PREMIAÇÃO — SETEMBRO/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loja TRANCOSO · as 4 metas somam · pagamento junto com o holerite de 05/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>META 4 — PERFUMARIA DA LOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Média mensal (mar-ago/26)</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>10923.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Meta = 130% da média</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Perfumaria vendida no mês</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Zerou o estoque? (SIM/NÃO)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>A LOJA BATEU A META 4?</t>
+        </is>
+      </c>
+      <c r="C9" s="28">
+        <f>IF(OR(AND(C7&lt;&gt;"",C7&gt;=C6),UPPER(C8)="SIM"),"SIM","NÃO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>FAIXA</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>META CHEIA</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>DIAS TRAB.</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>META AJUSTADA</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>VENDA REALIZADA</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>% DA META</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>PRÊMIO 80%</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>PRÊMIO 100%</t>
+        </is>
+      </c>
+      <c r="J11" s="29" t="inlineStr">
+        <is>
+          <t>PRÊMIO 120%</t>
+        </is>
+      </c>
+      <c r="K11" s="29" t="inlineStr">
+        <is>
+          <t>META 1 VOLUME</t>
+        </is>
+      </c>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>META 2 PROD. FOCO</t>
+        </is>
+      </c>
+      <c r="M11" s="29" t="inlineStr">
+        <is>
+          <t>PRÉ-VENC. VENDIDO</t>
+        </is>
+      </c>
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t>META PRÉ-V. FARMAC.</t>
+        </is>
+      </c>
+      <c r="O11" s="29" t="inlineStr">
+        <is>
+          <t>META 3 PRÉ-VENC.</t>
+        </is>
+      </c>
+      <c r="P11" s="29" t="inlineStr">
+        <is>
+          <t>META 4?</t>
+        </is>
+      </c>
+      <c r="Q11" s="29" t="inlineStr">
+        <is>
+          <t>COMISSÃO PERFUMARIA</t>
+        </is>
+      </c>
+      <c r="R11" s="29" t="inlineStr">
+        <is>
+          <t>META 4 PERFUM.</t>
+        </is>
+      </c>
+      <c r="S11" s="29" t="inlineStr">
+        <is>
+          <t>TOTAL PRÊMIOS</t>
+        </is>
+      </c>
+      <c r="T11" s="29" t="inlineStr">
+        <is>
+          <t>OBSERVAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>A - Vendedor pleno</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>31000</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25">
+        <f>ROUND(C12*IF(D12="",0,D12)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="31">
+        <f>IF(E12&gt;0,IF(F12="",0,F12)/E12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K12" s="32">
+        <f>IF(G12&gt;=1.2,J12,IF(G12&gt;=1,I12,IF(G12&gt;=0.8,H12,0)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="26" t="n"/>
+      <c r="N12" s="25" t="n"/>
+      <c r="O12" s="32">
+        <f>IF(M12&gt;=3000,300,IF(M12&gt;=2000,200,IF(M12&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="26" t="n"/>
+      <c r="R12" s="32">
+        <f>IF(AND(P12="SIM",$C$9="SIM"),IF(Q12="",0,Q12)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="33">
+        <f>ROUND(K12+IF(L12="",0,L12)+O12+R12,2)</f>
+        <v/>
+      </c>
+      <c r="T12" s="34" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/09: sem dias trabalhados, fica fora da apuração.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>A - Vendedor pleno</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" s="25">
+        <f>ROUND(C13*IF(D13="",0,D13)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="31">
+        <f>IF(E13&gt;0,IF(F13="",0,F13)/E13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K13" s="32">
+        <f>IF(G13&gt;=1.2,J13,IF(G13&gt;=1,I13,IF(G13&gt;=0.8,H13,0)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="25" t="n">
+        <v>940</v>
+      </c>
+      <c r="O13" s="32">
+        <f>IF(AND(M13&lt;&gt;"",M13&gt;=N13),150,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="32">
+        <f>IF(AND(P13="SIM",$C$9="SIM"),IF(Q13="",0,Q13)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S13" s="33">
+        <f>ROUND(K13+IF(L13="",0,L13)+O13+R13,2)</f>
+        <v/>
+      </c>
+      <c r="T13" s="34" t="inlineStr">
+        <is>
+          <t>Farmacêutico: na Meta 3 vale a regra própria (equipe + 30%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>A - Vendedor pleno</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="25">
+        <f>ROUND(C14*IF(D14="",0,D14)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F14" s="26" t="n"/>
+      <c r="G14" s="31">
+        <f>IF(E14&gt;0,IF(F14="",0,F14)/E14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="K14" s="32">
+        <f>IF(G14&gt;=1.2,J14,IF(G14&gt;=1,I14,IF(G14&gt;=0.8,H14,0)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="26" t="n"/>
+      <c r="M14" s="26" t="n"/>
+      <c r="N14" s="25" t="n"/>
+      <c r="O14" s="32">
+        <f>IF(M14&gt;=3000,300,IF(M14&gt;=2000,200,IF(M14&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="26" t="n"/>
+      <c r="R14" s="32">
+        <f>IF(AND(P14="SIM",$C$9="SIM"),IF(Q14="",0,Q14)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="33">
+        <f>ROUND(K14+IF(L14="",0,L14)+O14+R14,2)</f>
+        <v/>
+      </c>
+      <c r="T14" s="34" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>B - Meia jornada</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="25">
+        <f>ROUND(C15*IF(D15="",0,D15)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="31">
+        <f>IF(E15&gt;0,IF(F15="",0,F15)/E15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="K15" s="32">
+        <f>IF(G15&gt;=1.2,J15,IF(G15&gt;=1,I15,IF(G15&gt;=0.8,H15,0)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="26" t="n"/>
+      <c r="N15" s="25" t="n"/>
+      <c r="O15" s="32">
+        <f>IF(M15&gt;=3000,300,IF(M15&gt;=2000,200,IF(M15&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="30" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="Q15" s="26" t="n"/>
+      <c r="R15" s="32">
+        <f>IF(AND(P15="SIM",$C$9="SIM"),IF(Q15="",0,Q15)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="33">
+        <f>ROUND(K15+IF(L15="",0,L15)+O15+R15,2)</f>
+        <v/>
+      </c>
+      <c r="T15" s="34" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>B - Meia jornada</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" s="25">
+        <f>ROUND(C16*IF(D16="",0,D16)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="31">
+        <f>IF(E16&gt;0,IF(F16="",0,F16)/E16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>300</v>
+      </c>
+      <c r="K16" s="32">
+        <f>IF(G16&gt;=1.2,J16,IF(G16&gt;=1,I16,IF(G16&gt;=0.8,H16,0)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="26" t="n"/>
+      <c r="M16" s="26" t="n"/>
+      <c r="N16" s="25" t="n"/>
+      <c r="O16" s="32">
+        <f>IF(M16&gt;=3000,300,IF(M16&gt;=2000,200,IF(M16&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="30" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="Q16" s="26" t="n"/>
+      <c r="R16" s="32">
+        <f>IF(AND(P16="SIM",$C$9="SIM"),IF(Q16="",0,Q16)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="33">
+        <f>ROUND(K16+IF(L16="",0,L16)+O16+R16,2)</f>
+        <v/>
+      </c>
+      <c r="T16" s="34" t="inlineStr">
+        <is>
+          <t>Atestado de 02 a 08/09: 23 dias trabalhados. Ajustar se o atestado contar como dia trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="20">
+        <f>SUM(K12:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="20">
+        <f>SUM(L12:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="20">
+        <f>SUM(O12:O16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="20">
+        <f>SUM(R12:R16)</f>
+        <v/>
+      </c>
+      <c r="S17" s="20">
+        <f>SUM(S12:S16)</f>
+        <v/>
+      </c>
+      <c r="T17" s="18" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER (células amarelas):</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>VENDA REALIZADA: total vendido no mês pelo código do vendedor (InovaFarma, venda líquida). DIAS TRAB.: dias efetivamente trabalhados — a meta cai na mesma proporção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>META 1 — VOLUME: meta = média dos 3 últimos meses + 8%. 80% da meta paga o prêmio de 80%, 100% paga o de 100% e 120% paga o de 120%, conforme a faixa (A 150/250/500 · B 100/150/300 · C e D 50/80/150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>META 2 — PRODUTOS FOCO: lançar o valor apurado na semana (vitaminas da campanha, packs, injetáveis, coquetel, brinco, kit ressaca). ATENÇÃO: se o incentivo já vier no relatório do InovaFarma (linhas INCENTIVO do holerite), não lançar de novo aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>META 3 — PRÉ-VENCIDOS: escada mensal por vendedor (acima de R$ 1.000 = 100 · R$ 2.000 = 200 · R$ 3.000 = 300). Farmacêuticos têm regra própria: bateu a meta da coluna META PRÉ-V. FARMAC., recebe R$ 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>META 4 — PERFUMARIA 130%: meta da LOJA (bloco no topo). Se a loja bater 130% da média ou zerar o estoque, cada vendedora marcada recebe a comissão de perfumaria do mês mais R$ 50 fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>Os prêmios entram sozinhos nas linhas PRÊMIO META 1 a 4 do holerite. Fonte: planilha Metas_Equipe_Set2026_v2.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>TRANCOSO: se ainda valer a redução combinada para compensar a comissão dobrada, ajustar o prêmio manualmente no holerite.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A11:T16"/>
+  <mergeCells count="15">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A23:T23"/>
+    <mergeCell ref="A19:T19"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A22:T22"/>
+    <mergeCell ref="A26:T26"/>
+    <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A25:T25"/>
+    <mergeCell ref="A20:T20"/>
+    <mergeCell ref="A24:T24"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1758,42 +2457,42 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>ORIGEM / OBSERVAÇÃO</t>
         </is>
@@ -1805,68 +2504,68 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="39" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="39" t="n"/>
+      <c r="H5" s="39" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="41" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="41" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="41" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="41" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="42">
         <f>SUM(B6:F6)</f>
         <v/>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="43" t="inlineStr">
         <is>
           <t>Piso 2026 R$ 1.621,00; gerente conforme ago/2026. CONFERIR admissões, afastamentos e férias do mês.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
@@ -1874,35 +2573,35 @@
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="43" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="44">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
@@ -1910,34 +2609,34 @@
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="43" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="44">
         <f>ROUND('BASE INOVAFARMA SET.26'!F6*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="44">
         <f>ROUND('BASE INOVAFARMA SET.26'!F7*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="44">
         <f>ROUND('BASE INOVAFARMA SET.26'!F8*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="44">
         <f>ROUND('BASE INOVAFARMA SET.26'!F9*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
@@ -1945,28 +2644,28 @@
         <f>SUM(B9:F9)</f>
         <v/>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="H9" s="43" t="inlineStr">
         <is>
           <t>Apurado no InovaFarma (aba BASE INOVAFARMA SET.26), JÁ MULTIPLICADO POR 2 (multiplicador na aba PARÂMETROS). UILLIAN não recebe(m) comissão — lançado zero.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
       <c r="G10" s="20">
         <f>SUM(B10:F10)</f>
         <v/>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="43" t="inlineStr">
         <is>
           <t>PREENCHER: PDV antigos e complementos de comissão acordados, se houver.</t>
         </is>
@@ -2002,35 +2701,35 @@
         <f>SUM(B11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="43" t="inlineStr">
         <is>
           <t>Base do DSR junto com as horas extras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="45">
         <f>ROUND((B11+B8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="45">
         <f>ROUND((C11+C8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="45">
         <f>ROUND((D11+D8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="45">
         <f>ROUND((E11+E8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="45">
         <f>ROUND((F11+F8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
@@ -2038,695 +2737,797 @@
         <f>SUM(B12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
       <c r="G13" s="20">
         <f>SUM(B13:F13)</f>
         <v/>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="43" t="inlineStr">
         <is>
           <t>Conforme acordo da loja.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n"/>
-      <c r="C14" s="31" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="31" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="26" t="n"/>
       <c r="G14" s="20">
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Conforme apuração do caixa.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="28">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="B15" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="20">
         <f>SUM(B15:F15)</f>
         <v/>
       </c>
-      <c r="H15" s="29" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme a tabela de metas da loja (aba METAS da planilha original). Lançar já com a redução combinada para compensar o aumento da comissão dobrada.</t>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: venda do mês contra a meta individual (80% / 100% / 120%). Aplicar a redução combinada pela comissão dobrada, se ainda valer.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="31" t="n"/>
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="B16" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
       <c r="G16" s="20">
         <f>SUM(B16:F16)</f>
         <v/>
       </c>
-      <c r="H16" s="29" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme a apuração de pré-vencidos de setembro.</t>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: vitaminas, packs, injetáveis, coquetel, brinco e kit ressaca.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>FÉRIAS (DIAS GOZADOS)</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="B17" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
       <c r="G17" s="20">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="29" t="inlineStr">
-        <is>
-          <t>PREENCHER se houve férias no mês; informar o período.</t>
+      <c r="H17" s="43" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="n"/>
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="B18" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="44">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
       <c r="G18" s="20">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
-      <c r="H18" s="29" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+      <c r="H18" s="43" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="B19" s="30">
-        <f>'BASE INOVAFARMA SET.26'!G5</f>
-        <v/>
-      </c>
-      <c r="C19" s="30">
-        <f>'BASE INOVAFARMA SET.26'!G6</f>
-        <v/>
-      </c>
-      <c r="D19" s="30">
-        <f>'BASE INOVAFARMA SET.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E19" s="30">
-        <f>'BASE INOVAFARMA SET.26'!G8</f>
-        <v/>
-      </c>
-      <c r="F19" s="30">
-        <f>'BASE INOVAFARMA SET.26'!G9</f>
-        <v/>
-      </c>
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
       <c r="G19" s="20">
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
-      <c r="H19" s="29" t="inlineStr">
-        <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>PREENCHER se houve férias no mês; informar o período.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B20" s="30">
-        <f>'BASE INOVAFARMA SET.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C20" s="30">
-        <f>'BASE INOVAFARMA SET.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D20" s="30">
-        <f>'BASE INOVAFARMA SET.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E20" s="30">
-        <f>'BASE INOVAFARMA SET.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F20" s="30">
-        <f>'BASE INOVAFARMA SET.26'!H9</f>
-        <v/>
-      </c>
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="26" t="n"/>
       <c r="G20" s="20">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
-      <c r="H20" s="29" t="inlineStr">
-        <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+      <c r="H20" s="43" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B21" s="30">
-        <f>'BASE INOVAFARMA SET.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C21" s="30">
-        <f>'BASE INOVAFARMA SET.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D21" s="30">
-        <f>'BASE INOVAFARMA SET.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E21" s="30">
-        <f>'BASE INOVAFARMA SET.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F21" s="30">
-        <f>'BASE INOVAFARMA SET.26'!I9</f>
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="B21" s="44">
+        <f>'BASE INOVAFARMA SET.26'!G5</f>
+        <v/>
+      </c>
+      <c r="C21" s="44">
+        <f>'BASE INOVAFARMA SET.26'!G6</f>
+        <v/>
+      </c>
+      <c r="D21" s="44">
+        <f>'BASE INOVAFARMA SET.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E21" s="44">
+        <f>'BASE INOVAFARMA SET.26'!G8</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>'BASE INOVAFARMA SET.26'!G9</f>
         <v/>
       </c>
       <c r="G21" s="20">
         <f>SUM(B21:F21)</f>
         <v/>
       </c>
-      <c r="H21" s="29" t="inlineStr">
-        <is>
-          <t>Populares, oficinais e similar normal.</t>
+      <c r="H21" s="43" t="inlineStr">
+        <is>
+          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>SUM(B6:B21)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>SUM(C6:C21)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f>SUM(D6:D21)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="20">
-        <f>SUM(E6:E21)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F22" s="20">
-        <f>SUM(F6:F21)-F9-F10</f>
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>'BASE INOVAFARMA SET.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C22" s="44">
+        <f>'BASE INOVAFARMA SET.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D22" s="44">
+        <f>'BASE INOVAFARMA SET.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E22" s="44">
+        <f>'BASE INOVAFARMA SET.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F22" s="44">
+        <f>'BASE INOVAFARMA SET.26'!H9</f>
         <v/>
       </c>
       <c r="G22" s="20">
         <f>SUM(B22:F22)</f>
         <v/>
       </c>
-      <c r="H22" s="29" t="inlineStr">
-        <is>
-          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>DESCONTOS  (lançar com sinal negativo)</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
+      <c r="H22" s="43" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B23" s="44">
+        <f>'BASE INOVAFARMA SET.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C23" s="44">
+        <f>'BASE INOVAFARMA SET.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D23" s="44">
+        <f>'BASE INOVAFARMA SET.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E23" s="44">
+        <f>'BASE INOVAFARMA SET.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F23" s="44">
+        <f>'BASE INOVAFARMA SET.26'!I9</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>SUM(B23:F23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>Populares, oficinais e similar normal.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B24" s="20">
+        <f>SUM(B6:B23)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>SUM(C6:C23)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D24" s="20">
+        <f>SUM(D6:D23)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>SUM(E6:E23)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F24" s="20">
+        <f>SUM(F6:F23)-F9-F10</f>
+        <v/>
+      </c>
       <c r="G24" s="20">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
-      <c r="H24" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PREENCHER com os vales adiantados durante setembro. </t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B25" s="33">
-        <f>-(B19+B20+B21)</f>
-        <v/>
-      </c>
-      <c r="C25" s="33">
-        <f>-(C19+C20+C21)</f>
-        <v/>
-      </c>
-      <c r="D25" s="33">
-        <f>-(D19+D20+D21)</f>
-        <v/>
-      </c>
-      <c r="E25" s="33">
-        <f>-(E19+E20+E21)</f>
-        <v/>
-      </c>
-      <c r="F25" s="33">
-        <f>-(F19+F20+F21)</f>
-        <v/>
-      </c>
-      <c r="G25" s="28">
-        <f>SUM(B25:F25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="29" t="inlineStr">
-        <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
-        </is>
-      </c>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>DESCONTOS  (lançar com sinal negativo)</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="26" t="n"/>
       <c r="G26" s="20">
         <f>SUM(B26:F26)</f>
         <v/>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREENCHER com os vales adiantados durante setembro. </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B27" s="46">
+        <f>-(B21+B22+B23)</f>
+        <v/>
+      </c>
+      <c r="C27" s="46">
+        <f>-(C21+C22+C23)</f>
+        <v/>
+      </c>
+      <c r="D27" s="46">
+        <f>-(D21+D22+D23)</f>
+        <v/>
+      </c>
+      <c r="E27" s="46">
+        <f>-(E21+E22+E23)</f>
+        <v/>
+      </c>
+      <c r="F27" s="46">
+        <f>-(F21+F22+F23)</f>
+        <v/>
+      </c>
+      <c r="G27" s="42">
+        <f>SUM(B27:F27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="43" t="inlineStr">
+        <is>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="26" t="n"/>
+      <c r="G28" s="20">
+        <f>SUM(B28:F28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="43" t="inlineStr">
         <is>
           <t>PREENCHER conforme o convênio de setembro.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="20">
-        <f>SUM(B27:F27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="29" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o ponto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="28">
-        <f>SUM(B28:F28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="29" t="inlineStr">
-        <is>
-          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
       <c r="G29" s="20">
         <f>SUM(B29:F29)</f>
         <v/>
       </c>
-      <c r="H29" s="29" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+      <c r="H29" s="43" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="20">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="41" t="n"/>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="41" t="n"/>
+      <c r="G30" s="42">
         <f>SUM(B30:F30)</f>
         <v/>
       </c>
-      <c r="H30" s="29" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
+      <c r="H30" s="43" t="inlineStr">
+        <is>
+          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="B31" s="20">
-        <f>SUM(B24:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="20">
-        <f>SUM(C24:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="20">
-        <f>SUM(D24:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="20">
-        <f>SUM(E24:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f>SUM(F24:F30)</f>
-        <v/>
-      </c>
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
       <c r="G31" s="20">
         <f>SUM(B31:F31)</f>
         <v/>
       </c>
-      <c r="H31" s="29" t="inlineStr"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
+      <c r="H31" s="43" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+      <c r="G32" s="20">
+        <f>SUM(B32:F32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="43" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>LÍQUIDO A RECEBER (05/10/2026)</t>
-        </is>
-      </c>
-      <c r="B33" s="34">
-        <f>B22+B31</f>
-        <v/>
-      </c>
-      <c r="C33" s="34">
-        <f>C22+C31</f>
-        <v/>
-      </c>
-      <c r="D33" s="34">
-        <f>D22+D31</f>
-        <v/>
-      </c>
-      <c r="E33" s="34">
-        <f>E22+E31</f>
-        <v/>
-      </c>
-      <c r="F33" s="34">
-        <f>F22+F31</f>
-        <v/>
-      </c>
-      <c r="G33" s="34">
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="B33" s="20">
+        <f>SUM(B26:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>SUM(C26:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
+        <f>SUM(D26:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="20">
+        <f>SUM(E26:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="20">
+        <f>SUM(F26:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="20">
         <f>SUM(B33:F33)</f>
         <v/>
       </c>
-      <c r="H33" s="29" t="inlineStr">
-        <is>
-          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
-        </is>
-      </c>
+      <c r="H33" s="43" t="inlineStr"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="B34" s="39" t="n"/>
+      <c r="C34" s="39" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="39" t="n"/>
+      <c r="H34" s="39" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER (05/10/2026)</t>
+        </is>
+      </c>
+      <c r="B35" s="33">
+        <f>B24+B33</f>
+        <v/>
+      </c>
+      <c r="C35" s="33">
+        <f>C24+C33</f>
+        <v/>
+      </c>
+      <c r="D35" s="33">
+        <f>D24+D33</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
+        <f>E24+E33</f>
+        <v/>
+      </c>
+      <c r="F35" s="33">
+        <f>F24+F33</f>
+        <v/>
+      </c>
+      <c r="G35" s="33">
+        <f>SUM(B35:F35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="43" t="inlineStr">
+        <is>
+          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="B36" s="39" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>VALE TRANSPORTE (compra out/26)</t>
         </is>
       </c>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="20">
-        <f>SUM(B35:F35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+      <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
+      <c r="G37" s="20">
+        <f>SUM(B37:F37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">PREENCHER com as passagens compradas. </t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="20">
-        <f>SUM(B36:F36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="29" t="inlineStr">
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="26" t="n"/>
+      <c r="G38" s="20">
+        <f>SUM(B38:F38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="43" t="inlineStr">
         <is>
           <t>PREENCHER conforme escala de domingos e feriados.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="28">
-        <f>SUM(B37:F37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="29" t="inlineStr">
+      <c r="B39" s="41" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="42">
+        <f>SUM(B39:F39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. VALDICK: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B41" s="47" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
-        </is>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+          <t>Célula amarela, texto azul</t>
+        </is>
+      </c>
+      <c r="B42" s="47" t="inlineStr">
+        <is>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
+          <t>Célula laranja</t>
+        </is>
+      </c>
+      <c r="B43" s="47" t="inlineStr">
+        <is>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B44" s="47" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B45" s="47" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H37"/>
+  <autoFilter ref="A4:H39"/>
   <mergeCells count="7">
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2751,2674 +3552,2894 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D5" s="30">
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D5" s="44">
         <f>'HOLERITE SET.26'!B6</f>
         <v/>
       </c>
-      <c r="E5" s="36" t="n"/>
+      <c r="E5" s="48" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D6" s="30">
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D6" s="44">
         <f>'HOLERITE SET.26'!B7</f>
         <v/>
       </c>
-      <c r="E6" s="36" t="n"/>
+      <c r="E6" s="48" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D7" s="30">
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D7" s="44">
         <f>'HOLERITE SET.26'!B8</f>
         <v/>
       </c>
-      <c r="E7" s="36" t="n"/>
+      <c r="E7" s="48" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D8" s="30">
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D8" s="44">
         <f>'HOLERITE SET.26'!B11</f>
         <v/>
       </c>
-      <c r="E8" s="36" t="n"/>
+      <c r="E8" s="48" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D9" s="30">
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D9" s="44">
         <f>'HOLERITE SET.26'!B12</f>
         <v/>
       </c>
-      <c r="E9" s="36" t="n"/>
+      <c r="E9" s="48" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D10" s="30">
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D10" s="44">
         <f>'HOLERITE SET.26'!B13</f>
         <v/>
       </c>
-      <c r="E10" s="36" t="n"/>
+      <c r="E10" s="48" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D11" s="30">
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D11" s="44">
         <f>'HOLERITE SET.26'!B14</f>
         <v/>
       </c>
-      <c r="E11" s="36" t="n"/>
+      <c r="E11" s="48" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D12" s="30">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D12" s="44">
         <f>'HOLERITE SET.26'!B15</f>
         <v/>
       </c>
-      <c r="E12" s="36" t="n"/>
+      <c r="E12" s="48" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D13" s="30">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D13" s="44">
         <f>'HOLERITE SET.26'!B16</f>
         <v/>
       </c>
-      <c r="E13" s="36" t="n"/>
+      <c r="E13" s="48" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D14" s="44">
+        <f>'HOLERITE SET.26'!B17</f>
+        <v/>
+      </c>
+      <c r="E14" s="48" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D15" s="44">
+        <f>'HOLERITE SET.26'!B18</f>
+        <v/>
+      </c>
+      <c r="E15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D14" s="30">
-        <f>'HOLERITE SET.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D16" s="44">
+        <f>'HOLERITE SET.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E16" s="48" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D15" s="30">
-        <f>'HOLERITE SET.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D17" s="44">
+        <f>'HOLERITE SET.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E17" s="48" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D16" s="30">
-        <f>'HOLERITE SET.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D18" s="44">
+        <f>'HOLERITE SET.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E18" s="48" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D17" s="30">
-        <f>'HOLERITE SET.26'!B20</f>
-        <v/>
-      </c>
-      <c r="E17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D19" s="44">
+        <f>'HOLERITE SET.26'!B22</f>
+        <v/>
+      </c>
+      <c r="E19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D18" s="30">
-        <f>'HOLERITE SET.26'!B21</f>
-        <v/>
-      </c>
-      <c r="E18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D20" s="44">
+        <f>'HOLERITE SET.26'!B23</f>
+        <v/>
+      </c>
+      <c r="E20" s="48" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C21" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D19" s="38">
-        <f>'HOLERITE SET.26'!B22</f>
-        <v/>
-      </c>
-      <c r="E19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="D21" s="50">
+        <f>'HOLERITE SET.26'!B24</f>
+        <v/>
+      </c>
+      <c r="E21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C22" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D20" s="30">
-        <f>'HOLERITE SET.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="D22" s="44">
+        <f>'HOLERITE SET.26'!B26</f>
+        <v/>
+      </c>
+      <c r="E22" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D21" s="30">
-        <f>'HOLERITE SET.26'!B25</f>
-        <v/>
-      </c>
-      <c r="E21" s="36" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="D23" s="44">
+        <f>'HOLERITE SET.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E23" s="48" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C24" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="30">
-        <f>'HOLERITE SET.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="36" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="D24" s="44">
+        <f>'HOLERITE SET.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E24" s="48" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="30">
-        <f>'HOLERITE SET.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="36" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="D25" s="44">
+        <f>'HOLERITE SET.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E25" s="48" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C26" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="30">
-        <f>'HOLERITE SET.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="36" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="D26" s="44">
+        <f>'HOLERITE SET.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E26" s="48" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D25" s="30">
-        <f>'HOLERITE SET.26'!B29</f>
-        <v/>
-      </c>
-      <c r="E25" s="36" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="D27" s="44">
+        <f>'HOLERITE SET.26'!B31</f>
+        <v/>
+      </c>
+      <c r="E27" s="48" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C28" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D26" s="30">
-        <f>'HOLERITE SET.26'!B30</f>
-        <v/>
-      </c>
-      <c r="E26" s="36" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="D28" s="44">
+        <f>'HOLERITE SET.26'!B32</f>
+        <v/>
+      </c>
+      <c r="E28" s="48" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C29" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D27" s="38">
-        <f>'HOLERITE SET.26'!B31</f>
-        <v/>
-      </c>
-      <c r="E27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="D29" s="50">
+        <f>'HOLERITE SET.26'!B33</f>
+        <v/>
+      </c>
+      <c r="E29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C30" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D28" s="41">
-        <f>'HOLERITE SET.26'!B33</f>
-        <v/>
-      </c>
-      <c r="E28" s="42" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="D30" s="53">
+        <f>'HOLERITE SET.26'!B35</f>
+        <v/>
+      </c>
+      <c r="E30" s="54" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D30" s="30">
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D32" s="44">
         <f>'HOLERITE SET.26'!C6</f>
         <v/>
       </c>
-      <c r="E30" s="36" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="E32" s="48" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D31" s="30">
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D33" s="44">
         <f>'HOLERITE SET.26'!C7</f>
         <v/>
       </c>
-      <c r="E31" s="36" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="E33" s="48" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D32" s="30">
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D34" s="44">
         <f>'HOLERITE SET.26'!C8</f>
         <v/>
       </c>
-      <c r="E32" s="36" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="E34" s="48" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D33" s="30">
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D35" s="44">
         <f>'HOLERITE SET.26'!C11</f>
         <v/>
       </c>
-      <c r="E33" s="36" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="E35" s="48" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D34" s="30">
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D36" s="44">
         <f>'HOLERITE SET.26'!C12</f>
         <v/>
       </c>
-      <c r="E34" s="36" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="E36" s="48" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D35" s="30">
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D37" s="44">
         <f>'HOLERITE SET.26'!C13</f>
         <v/>
       </c>
-      <c r="E35" s="36" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="E37" s="48" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D36" s="30">
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D38" s="44">
         <f>'HOLERITE SET.26'!C14</f>
         <v/>
       </c>
-      <c r="E36" s="36" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="E38" s="48" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D37" s="30">
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D39" s="44">
         <f>'HOLERITE SET.26'!C15</f>
         <v/>
       </c>
-      <c r="E37" s="36" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="E39" s="48" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D38" s="30">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D40" s="44">
         <f>'HOLERITE SET.26'!C16</f>
         <v/>
       </c>
-      <c r="E38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="E40" s="48" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D41" s="44">
+        <f>'HOLERITE SET.26'!C17</f>
+        <v/>
+      </c>
+      <c r="E41" s="48" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D42" s="44">
+        <f>'HOLERITE SET.26'!C18</f>
+        <v/>
+      </c>
+      <c r="E42" s="48" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D39" s="30">
-        <f>'HOLERITE SET.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E39" s="36" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D43" s="44">
+        <f>'HOLERITE SET.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E43" s="48" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D40" s="30">
-        <f>'HOLERITE SET.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E40" s="36" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D44" s="44">
+        <f>'HOLERITE SET.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E44" s="48" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D41" s="30">
-        <f>'HOLERITE SET.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E41" s="36" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D45" s="44">
+        <f>'HOLERITE SET.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E45" s="48" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D42" s="30">
-        <f>'HOLERITE SET.26'!C20</f>
-        <v/>
-      </c>
-      <c r="E42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D46" s="44">
+        <f>'HOLERITE SET.26'!C22</f>
+        <v/>
+      </c>
+      <c r="E46" s="48" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D43" s="30">
-        <f>'HOLERITE SET.26'!C21</f>
-        <v/>
-      </c>
-      <c r="E43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D47" s="44">
+        <f>'HOLERITE SET.26'!C23</f>
+        <v/>
+      </c>
+      <c r="E47" s="48" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="49" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B48" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C44" s="37" t="inlineStr">
+      <c r="C48" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D44" s="38">
-        <f>'HOLERITE SET.26'!C22</f>
-        <v/>
-      </c>
-      <c r="E44" s="18" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="D48" s="50">
+        <f>'HOLERITE SET.26'!C24</f>
+        <v/>
+      </c>
+      <c r="E48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C49" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D45" s="30">
-        <f>'HOLERITE SET.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E45" s="36" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="D49" s="44">
+        <f>'HOLERITE SET.26'!C26</f>
+        <v/>
+      </c>
+      <c r="E49" s="48" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C50" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D46" s="30">
-        <f>'HOLERITE SET.26'!C25</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="D50" s="44">
+        <f>'HOLERITE SET.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E50" s="48" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C51" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D47" s="30">
-        <f>'HOLERITE SET.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E47" s="36" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="D51" s="44">
+        <f>'HOLERITE SET.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E51" s="48" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C52" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D48" s="30">
-        <f>'HOLERITE SET.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="D52" s="44">
+        <f>'HOLERITE SET.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E52" s="48" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C53" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D49" s="30">
-        <f>'HOLERITE SET.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="D53" s="44">
+        <f>'HOLERITE SET.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E53" s="48" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C54" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D50" s="30">
-        <f>'HOLERITE SET.26'!C29</f>
-        <v/>
-      </c>
-      <c r="E50" s="36" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="D54" s="44">
+        <f>'HOLERITE SET.26'!C31</f>
+        <v/>
+      </c>
+      <c r="E54" s="48" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="40" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
+      <c r="C55" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D51" s="30">
-        <f>'HOLERITE SET.26'!C30</f>
-        <v/>
-      </c>
-      <c r="E51" s="36" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="37" t="inlineStr">
+      <c r="D55" s="44">
+        <f>'HOLERITE SET.26'!C32</f>
+        <v/>
+      </c>
+      <c r="E55" s="48" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="49" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B56" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C52" s="37" t="inlineStr">
+      <c r="C56" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D52" s="38">
-        <f>'HOLERITE SET.26'!C31</f>
-        <v/>
-      </c>
-      <c r="E52" s="18" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="39" t="inlineStr">
+      <c r="D56" s="50">
+        <f>'HOLERITE SET.26'!C33</f>
+        <v/>
+      </c>
+      <c r="E56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="B53" s="40" t="inlineStr">
+      <c r="B57" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C57" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D53" s="41">
-        <f>'HOLERITE SET.26'!C33</f>
-        <v/>
-      </c>
-      <c r="E53" s="42" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="D57" s="53">
+        <f>'HOLERITE SET.26'!C35</f>
+        <v/>
+      </c>
+      <c r="E57" s="54" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D55" s="30">
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D59" s="44">
         <f>'HOLERITE SET.26'!D6</f>
         <v/>
       </c>
-      <c r="E55" s="36" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="E59" s="48" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D56" s="30">
+      <c r="C60" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D60" s="44">
         <f>'HOLERITE SET.26'!D7</f>
         <v/>
       </c>
-      <c r="E56" s="36" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="E60" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D57" s="30">
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D61" s="44">
         <f>'HOLERITE SET.26'!D8</f>
         <v/>
       </c>
-      <c r="E57" s="36" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="E61" s="48" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D58" s="30">
+      <c r="C62" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D62" s="44">
         <f>'HOLERITE SET.26'!D11</f>
         <v/>
       </c>
-      <c r="E58" s="36" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="E62" s="48" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B59" s="26" t="inlineStr">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D59" s="30">
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D63" s="44">
         <f>'HOLERITE SET.26'!D12</f>
         <v/>
       </c>
-      <c r="E59" s="36" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="E63" s="48" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D60" s="30">
+      <c r="C64" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D64" s="44">
         <f>'HOLERITE SET.26'!D13</f>
         <v/>
       </c>
-      <c r="E60" s="36" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="E64" s="48" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D61" s="30">
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D65" s="44">
         <f>'HOLERITE SET.26'!D14</f>
         <v/>
       </c>
-      <c r="E61" s="36" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="E65" s="48" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D62" s="30">
+      <c r="B66" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C66" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D66" s="44">
         <f>'HOLERITE SET.26'!D15</f>
         <v/>
       </c>
-      <c r="E62" s="36" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="E66" s="48" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D63" s="30">
+      <c r="B67" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D67" s="44">
         <f>'HOLERITE SET.26'!D16</f>
         <v/>
       </c>
-      <c r="E63" s="36" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="E67" s="48" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C68" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D68" s="44">
+        <f>'HOLERITE SET.26'!D17</f>
+        <v/>
+      </c>
+      <c r="E68" s="48" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="40" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B69" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D69" s="44">
+        <f>'HOLERITE SET.26'!D18</f>
+        <v/>
+      </c>
+      <c r="E69" s="48" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="40" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D64" s="30">
-        <f>'HOLERITE SET.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E64" s="36" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="26" t="inlineStr">
+      <c r="C70" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D70" s="44">
+        <f>'HOLERITE SET.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E70" s="48" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D65" s="30">
-        <f>'HOLERITE SET.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E65" s="36" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D71" s="44">
+        <f>'HOLERITE SET.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E71" s="48" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D66" s="30">
-        <f>'HOLERITE SET.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E66" s="36" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D72" s="44">
+        <f>'HOLERITE SET.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E72" s="48" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B67" s="26" t="inlineStr">
+      <c r="B73" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D67" s="30">
-        <f>'HOLERITE SET.26'!D20</f>
-        <v/>
-      </c>
-      <c r="E67" s="36" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D73" s="44">
+        <f>'HOLERITE SET.26'!D22</f>
+        <v/>
+      </c>
+      <c r="E73" s="48" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D68" s="30">
-        <f>'HOLERITE SET.26'!D21</f>
-        <v/>
-      </c>
-      <c r="E68" s="36" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="C74" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D74" s="44">
+        <f>'HOLERITE SET.26'!D23</f>
+        <v/>
+      </c>
+      <c r="E74" s="48" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="49" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B69" s="37" t="inlineStr">
+      <c r="B75" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C69" s="37" t="inlineStr">
+      <c r="C75" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D69" s="38">
-        <f>'HOLERITE SET.26'!D22</f>
-        <v/>
-      </c>
-      <c r="E69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="D75" s="50">
+        <f>'HOLERITE SET.26'!D24</f>
+        <v/>
+      </c>
+      <c r="E75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C76" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D70" s="30">
-        <f>'HOLERITE SET.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E70" s="36" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="D76" s="44">
+        <f>'HOLERITE SET.26'!D26</f>
+        <v/>
+      </c>
+      <c r="E76" s="48" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B77" s="40" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D71" s="30">
-        <f>'HOLERITE SET.26'!D25</f>
-        <v/>
-      </c>
-      <c r="E71" s="36" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="D77" s="44">
+        <f>'HOLERITE SET.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E77" s="48" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B72" s="26" t="inlineStr">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="C78" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D72" s="30">
-        <f>'HOLERITE SET.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E72" s="36" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="D78" s="44">
+        <f>'HOLERITE SET.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E78" s="48" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B73" s="26" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C73" s="26" t="inlineStr">
+      <c r="C79" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D73" s="30">
-        <f>'HOLERITE SET.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E73" s="36" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="D79" s="44">
+        <f>'HOLERITE SET.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E79" s="48" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B74" s="26" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C74" s="26" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D74" s="30">
-        <f>'HOLERITE SET.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E74" s="36" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="D80" s="44">
+        <f>'HOLERITE SET.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E80" s="48" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B81" s="40" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C81" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D75" s="30">
-        <f>'HOLERITE SET.26'!D29</f>
-        <v/>
-      </c>
-      <c r="E75" s="36" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="D81" s="44">
+        <f>'HOLERITE SET.26'!D31</f>
+        <v/>
+      </c>
+      <c r="E81" s="48" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="40" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B76" s="26" t="inlineStr">
+      <c r="B82" s="40" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C76" s="26" t="inlineStr">
+      <c r="C82" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D76" s="30">
-        <f>'HOLERITE SET.26'!D30</f>
-        <v/>
-      </c>
-      <c r="E76" s="36" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="D82" s="44">
+        <f>'HOLERITE SET.26'!D32</f>
+        <v/>
+      </c>
+      <c r="E82" s="48" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="49" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B77" s="37" t="inlineStr">
+      <c r="B83" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C77" s="37" t="inlineStr">
+      <c r="C83" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D77" s="38">
-        <f>'HOLERITE SET.26'!D31</f>
-        <v/>
-      </c>
-      <c r="E77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="inlineStr">
+      <c r="D83" s="50">
+        <f>'HOLERITE SET.26'!D33</f>
+        <v/>
+      </c>
+      <c r="E83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B78" s="40" t="inlineStr">
+      <c r="B84" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C84" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D78" s="41">
-        <f>'HOLERITE SET.26'!D33</f>
-        <v/>
-      </c>
-      <c r="E78" s="42" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="D84" s="53">
+        <f>'HOLERITE SET.26'!D35</f>
+        <v/>
+      </c>
+      <c r="E84" s="54" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B80" s="26" t="inlineStr">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C80" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D80" s="30">
+      <c r="C86" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D86" s="44">
         <f>'HOLERITE SET.26'!E6</f>
         <v/>
       </c>
-      <c r="E80" s="36" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="E86" s="48" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B81" s="26" t="inlineStr">
+      <c r="B87" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C81" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D81" s="30">
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D87" s="44">
         <f>'HOLERITE SET.26'!E7</f>
         <v/>
       </c>
-      <c r="E81" s="36" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="E87" s="48" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B82" s="26" t="inlineStr">
+      <c r="B88" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D82" s="30">
+      <c r="C88" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D88" s="44">
         <f>'HOLERITE SET.26'!E8</f>
         <v/>
       </c>
-      <c r="E82" s="36" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="E88" s="48" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B83" s="26" t="inlineStr">
+      <c r="B89" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C83" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D83" s="30">
+      <c r="C89" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D89" s="44">
         <f>'HOLERITE SET.26'!E11</f>
         <v/>
       </c>
-      <c r="E83" s="36" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="E89" s="48" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B84" s="26" t="inlineStr">
+      <c r="B90" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D84" s="30">
+      <c r="C90" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D90" s="44">
         <f>'HOLERITE SET.26'!E12</f>
         <v/>
       </c>
-      <c r="E84" s="36" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="E90" s="48" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B85" s="26" t="inlineStr">
+      <c r="B91" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C85" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D85" s="30">
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D91" s="44">
         <f>'HOLERITE SET.26'!E13</f>
         <v/>
       </c>
-      <c r="E85" s="36" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="E91" s="48" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B86" s="26" t="inlineStr">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C86" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D86" s="30">
+      <c r="C92" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D92" s="44">
         <f>'HOLERITE SET.26'!E14</f>
         <v/>
       </c>
-      <c r="E86" s="36" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="26" t="inlineStr">
+      <c r="E92" s="48" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B87" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C87" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D87" s="30">
+      <c r="B93" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D93" s="44">
         <f>'HOLERITE SET.26'!E15</f>
         <v/>
       </c>
-      <c r="E87" s="36" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="E93" s="48" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B88" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D88" s="30">
+      <c r="B94" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C94" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D94" s="44">
         <f>'HOLERITE SET.26'!E16</f>
         <v/>
       </c>
-      <c r="E88" s="36" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="26" t="inlineStr">
+      <c r="E94" s="48" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B89" s="26" t="inlineStr">
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D95" s="44">
+        <f>'HOLERITE SET.26'!E17</f>
+        <v/>
+      </c>
+      <c r="E95" s="48" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="40" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B96" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C96" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D96" s="44">
+        <f>'HOLERITE SET.26'!E18</f>
+        <v/>
+      </c>
+      <c r="E96" s="48" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="40" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B97" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C89" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D89" s="30">
-        <f>'HOLERITE SET.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E89" s="36" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D97" s="44">
+        <f>'HOLERITE SET.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E97" s="48" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B90" s="26" t="inlineStr">
+      <c r="B98" s="40" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C90" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D90" s="30">
-        <f>'HOLERITE SET.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E90" s="36" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="26" t="inlineStr">
+      <c r="C98" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D98" s="44">
+        <f>'HOLERITE SET.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E98" s="48" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B91" s="26" t="inlineStr">
+      <c r="B99" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C91" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D91" s="30">
-        <f>'HOLERITE SET.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E91" s="36" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D99" s="44">
+        <f>'HOLERITE SET.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E99" s="48" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B92" s="26" t="inlineStr">
+      <c r="B100" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C92" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D92" s="30">
-        <f>'HOLERITE SET.26'!E20</f>
-        <v/>
-      </c>
-      <c r="E92" s="36" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="C100" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D100" s="44">
+        <f>'HOLERITE SET.26'!E22</f>
+        <v/>
+      </c>
+      <c r="E100" s="48" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B93" s="26" t="inlineStr">
+      <c r="B101" s="40" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C93" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D93" s="30">
-        <f>'HOLERITE SET.26'!E21</f>
-        <v/>
-      </c>
-      <c r="E93" s="36" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="37" t="inlineStr">
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D101" s="44">
+        <f>'HOLERITE SET.26'!E23</f>
+        <v/>
+      </c>
+      <c r="E101" s="48" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="49" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B94" s="37" t="inlineStr">
+      <c r="B102" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C94" s="37" t="inlineStr">
+      <c r="C102" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D94" s="38">
-        <f>'HOLERITE SET.26'!E22</f>
-        <v/>
-      </c>
-      <c r="E94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="26" t="inlineStr">
+      <c r="D102" s="50">
+        <f>'HOLERITE SET.26'!E24</f>
+        <v/>
+      </c>
+      <c r="E102" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B95" s="26" t="inlineStr">
+      <c r="B103" s="40" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C95" s="26" t="inlineStr">
+      <c r="C103" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D95" s="30">
-        <f>'HOLERITE SET.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E95" s="36" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="D103" s="44">
+        <f>'HOLERITE SET.26'!E26</f>
+        <v/>
+      </c>
+      <c r="E103" s="48" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B96" s="26" t="inlineStr">
+      <c r="B104" s="40" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C96" s="26" t="inlineStr">
+      <c r="C104" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D96" s="30">
-        <f>'HOLERITE SET.26'!E25</f>
-        <v/>
-      </c>
-      <c r="E96" s="36" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="26" t="inlineStr">
+      <c r="D104" s="44">
+        <f>'HOLERITE SET.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E104" s="48" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B97" s="26" t="inlineStr">
+      <c r="B105" s="40" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C97" s="26" t="inlineStr">
+      <c r="C105" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D97" s="30">
-        <f>'HOLERITE SET.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E97" s="36" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="D105" s="44">
+        <f>'HOLERITE SET.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E105" s="48" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="B106" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C98" s="26" t="inlineStr">
+      <c r="C106" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D98" s="30">
-        <f>'HOLERITE SET.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E98" s="36" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="D106" s="44">
+        <f>'HOLERITE SET.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E106" s="48" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B107" s="40" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C99" s="26" t="inlineStr">
+      <c r="C107" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D99" s="30">
-        <f>'HOLERITE SET.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E99" s="36" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="D107" s="44">
+        <f>'HOLERITE SET.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E107" s="48" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B100" s="26" t="inlineStr">
+      <c r="B108" s="40" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C100" s="26" t="inlineStr">
+      <c r="C108" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D100" s="30">
-        <f>'HOLERITE SET.26'!E29</f>
-        <v/>
-      </c>
-      <c r="E100" s="36" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+      <c r="D108" s="44">
+        <f>'HOLERITE SET.26'!E31</f>
+        <v/>
+      </c>
+      <c r="E108" s="48" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="40" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B109" s="40" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C101" s="26" t="inlineStr">
+      <c r="C109" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D101" s="30">
-        <f>'HOLERITE SET.26'!E30</f>
-        <v/>
-      </c>
-      <c r="E101" s="36" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="37" t="inlineStr">
+      <c r="D109" s="44">
+        <f>'HOLERITE SET.26'!E32</f>
+        <v/>
+      </c>
+      <c r="E109" s="48" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="49" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B102" s="37" t="inlineStr">
+      <c r="B110" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C102" s="37" t="inlineStr">
+      <c r="C110" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="38">
-        <f>'HOLERITE SET.26'!E31</f>
-        <v/>
-      </c>
-      <c r="E102" s="18" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="39" t="inlineStr">
+      <c r="D110" s="50">
+        <f>'HOLERITE SET.26'!E33</f>
+        <v/>
+      </c>
+      <c r="E110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="B103" s="40" t="inlineStr">
+      <c r="B111" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C103" s="40" t="inlineStr">
+      <c r="C111" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D103" s="41">
-        <f>'HOLERITE SET.26'!E33</f>
-        <v/>
-      </c>
-      <c r="E103" s="42" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="26" t="inlineStr">
+      <c r="D111" s="53">
+        <f>'HOLERITE SET.26'!E35</f>
+        <v/>
+      </c>
+      <c r="E111" s="54" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B105" s="26" t="inlineStr">
+      <c r="B113" s="40" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C105" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D105" s="30">
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D113" s="44">
         <f>'HOLERITE SET.26'!F6</f>
         <v/>
       </c>
-      <c r="E105" s="36" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="E113" s="48" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B106" s="26" t="inlineStr">
+      <c r="B114" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C106" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D106" s="30">
+      <c r="C114" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D114" s="44">
         <f>'HOLERITE SET.26'!F7</f>
         <v/>
       </c>
-      <c r="E106" s="36" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="26" t="inlineStr">
+      <c r="E114" s="48" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B107" s="26" t="inlineStr">
+      <c r="B115" s="40" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C107" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D107" s="30">
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D115" s="44">
         <f>'HOLERITE SET.26'!F8</f>
         <v/>
       </c>
-      <c r="E107" s="36" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="26" t="inlineStr">
+      <c r="E115" s="48" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B108" s="26" t="inlineStr">
+      <c r="B116" s="40" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C108" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D108" s="30">
+      <c r="C116" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D116" s="44">
         <f>'HOLERITE SET.26'!F11</f>
         <v/>
       </c>
-      <c r="E108" s="36" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="26" t="inlineStr">
+      <c r="E116" s="48" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B109" s="26" t="inlineStr">
+      <c r="B117" s="40" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C109" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D109" s="30">
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D117" s="44">
         <f>'HOLERITE SET.26'!F12</f>
         <v/>
       </c>
-      <c r="E109" s="36" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="26" t="inlineStr">
+      <c r="E117" s="48" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B110" s="26" t="inlineStr">
+      <c r="B118" s="40" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C110" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D110" s="30">
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D118" s="44">
         <f>'HOLERITE SET.26'!F13</f>
         <v/>
       </c>
-      <c r="E110" s="36" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="26" t="inlineStr">
+      <c r="E118" s="48" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B111" s="26" t="inlineStr">
+      <c r="B119" s="40" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C111" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D111" s="30">
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D119" s="44">
         <f>'HOLERITE SET.26'!F14</f>
         <v/>
       </c>
-      <c r="E111" s="36" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="E119" s="48" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B112" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C112" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D112" s="30">
+      <c r="B120" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D120" s="44">
         <f>'HOLERITE SET.26'!F15</f>
         <v/>
       </c>
-      <c r="E112" s="36" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="26" t="inlineStr">
+      <c r="E120" s="48" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B113" s="26" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C113" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D113" s="30">
+      <c r="B121" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D121" s="44">
         <f>'HOLERITE SET.26'!F16</f>
         <v/>
       </c>
-      <c r="E113" s="36" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="E121" s="48" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B114" s="26" t="inlineStr">
+      <c r="B122" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C122" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D122" s="44">
+        <f>'HOLERITE SET.26'!F17</f>
+        <v/>
+      </c>
+      <c r="E122" s="48" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="40" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B123" s="40" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D123" s="44">
+        <f>'HOLERITE SET.26'!F18</f>
+        <v/>
+      </c>
+      <c r="E123" s="48" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="40" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B124" s="40" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C114" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D114" s="30">
-        <f>'HOLERITE SET.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E114" s="36" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="26" t="inlineStr">
+      <c r="C124" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D124" s="44">
+        <f>'HOLERITE SET.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E124" s="48" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B115" s="26" t="inlineStr">
+      <c r="B125" s="40" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C115" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D115" s="30">
-        <f>'HOLERITE SET.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E115" s="36" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D125" s="44">
+        <f>'HOLERITE SET.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E125" s="48" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B116" s="26" t="inlineStr">
+      <c r="B126" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C116" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D116" s="30">
-        <f>'HOLERITE SET.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E116" s="36" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="26" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D126" s="44">
+        <f>'HOLERITE SET.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E126" s="48" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B117" s="26" t="inlineStr">
+      <c r="B127" s="40" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C117" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D117" s="30">
-        <f>'HOLERITE SET.26'!F20</f>
-        <v/>
-      </c>
-      <c r="E117" s="36" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="C127" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D127" s="44">
+        <f>'HOLERITE SET.26'!F22</f>
+        <v/>
+      </c>
+      <c r="E127" s="48" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B118" s="26" t="inlineStr">
+      <c r="B128" s="40" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C118" s="26" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D118" s="30">
-        <f>'HOLERITE SET.26'!F21</f>
-        <v/>
-      </c>
-      <c r="E118" s="36" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="C128" s="40" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D128" s="44">
+        <f>'HOLERITE SET.26'!F23</f>
+        <v/>
+      </c>
+      <c r="E128" s="48" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="49" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B119" s="37" t="inlineStr">
+      <c r="B129" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C119" s="37" t="inlineStr">
+      <c r="C129" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D119" s="38">
-        <f>'HOLERITE SET.26'!F22</f>
-        <v/>
-      </c>
-      <c r="E119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="26" t="inlineStr">
+      <c r="D129" s="50">
+        <f>'HOLERITE SET.26'!F24</f>
+        <v/>
+      </c>
+      <c r="E129" s="18" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B120" s="26" t="inlineStr">
+      <c r="B130" s="40" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C120" s="26" t="inlineStr">
+      <c r="C130" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D120" s="30">
-        <f>'HOLERITE SET.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E120" s="36" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="26" t="inlineStr">
+      <c r="D130" s="44">
+        <f>'HOLERITE SET.26'!F26</f>
+        <v/>
+      </c>
+      <c r="E130" s="48" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B121" s="26" t="inlineStr">
+      <c r="B131" s="40" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C121" s="26" t="inlineStr">
+      <c r="C131" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D121" s="30">
-        <f>'HOLERITE SET.26'!F25</f>
-        <v/>
-      </c>
-      <c r="E121" s="36" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="D131" s="44">
+        <f>'HOLERITE SET.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E131" s="48" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B122" s="26" t="inlineStr">
+      <c r="B132" s="40" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C122" s="26" t="inlineStr">
+      <c r="C132" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D122" s="30">
-        <f>'HOLERITE SET.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E122" s="36" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="26" t="inlineStr">
+      <c r="D132" s="44">
+        <f>'HOLERITE SET.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E132" s="48" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B123" s="26" t="inlineStr">
+      <c r="B133" s="40" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C123" s="26" t="inlineStr">
+      <c r="C133" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D123" s="30">
-        <f>'HOLERITE SET.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E123" s="36" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="D133" s="44">
+        <f>'HOLERITE SET.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E133" s="48" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B124" s="26" t="inlineStr">
+      <c r="B134" s="40" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C124" s="26" t="inlineStr">
+      <c r="C134" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D124" s="30">
-        <f>'HOLERITE SET.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E124" s="36" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="26" t="inlineStr">
+      <c r="D134" s="44">
+        <f>'HOLERITE SET.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E134" s="48" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B135" s="40" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C125" s="26" t="inlineStr">
+      <c r="C135" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D125" s="30">
-        <f>'HOLERITE SET.26'!F29</f>
-        <v/>
-      </c>
-      <c r="E125" s="36" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="26" t="inlineStr">
+      <c r="D135" s="44">
+        <f>'HOLERITE SET.26'!F31</f>
+        <v/>
+      </c>
+      <c r="E135" s="48" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="40" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B126" s="26" t="inlineStr">
+      <c r="B136" s="40" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C126" s="26" t="inlineStr">
+      <c r="C136" s="40" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D126" s="30">
-        <f>'HOLERITE SET.26'!F30</f>
-        <v/>
-      </c>
-      <c r="E126" s="36" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="37" t="inlineStr">
+      <c r="D136" s="44">
+        <f>'HOLERITE SET.26'!F32</f>
+        <v/>
+      </c>
+      <c r="E136" s="48" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="49" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B127" s="37" t="inlineStr">
+      <c r="B137" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C127" s="37" t="inlineStr">
+      <c r="C137" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D127" s="38">
-        <f>'HOLERITE SET.26'!F31</f>
-        <v/>
-      </c>
-      <c r="E127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="39" t="inlineStr">
+      <c r="D137" s="50">
+        <f>'HOLERITE SET.26'!F33</f>
+        <v/>
+      </c>
+      <c r="E137" s="18" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B128" s="40" t="inlineStr">
+      <c r="B138" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C128" s="40" t="inlineStr">
+      <c r="C138" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D128" s="41">
-        <f>'HOLERITE SET.26'!F33</f>
-        <v/>
-      </c>
-      <c r="E128" s="42" t="n"/>
+      <c r="D138" s="53">
+        <f>'HOLERITE SET.26'!F35</f>
+        <v/>
+      </c>
+      <c r="E138" s="54" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E128"/>
+  <autoFilter ref="A4:E138"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -5427,13 +6448,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5457,17 +6478,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Escolha o colaborador:</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Troque o nome aqui e a tabela abaixo muda sozinha — é o relatório para mandar para cada um.</t>
         </is>
@@ -5479,376 +6500,398 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="25" t="n"/>
+      <c r="C6" s="39" t="n"/>
+      <c r="D6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$7:$F$7,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$8:$F$8,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$11:$F$11,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$12:$F$12,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$13:$F$13,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$14:$F$14,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral</t>
-        </is>
-      </c>
-      <c r="C14" s="30">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Prêmio meta 1 — volume</t>
+        </is>
+      </c>
+      <c r="C14" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$15:$F$15,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Prêmio pré-vencidos</t>
-        </is>
-      </c>
-      <c r="C15" s="30">
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>Prêmio meta 2 — produtos foco</t>
+        </is>
+      </c>
+      <c r="C15" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$16:$F$16,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>Prêmio meta 3 — pré-vencidos</t>
+        </is>
+      </c>
+      <c r="C16" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Prêmio meta 4 — perfumaria</t>
+        </is>
+      </c>
+      <c r="C17" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Férias</t>
         </is>
       </c>
-      <c r="C16" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="C18" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>1/3 constitucional de férias</t>
         </is>
       </c>
-      <c r="C17" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="C19" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Incentivo aplicações</t>
         </is>
       </c>
-      <c r="C18" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="C20" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Incentivo vitaminas</t>
         </is>
       </c>
-      <c r="C19" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="C21" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Outros incentivos</t>
         </is>
       </c>
-      <c r="C20" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="19" t="inlineStr">
+      <c r="C22" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$23:$F$23,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="38">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="C23" s="50">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="26" t="inlineStr">
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Adiantamento salarial / vales</t>
         </is>
       </c>
-      <c r="C23" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="26" t="inlineStr">
+      <c r="C25" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$F$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Adiantamento de incentivos e aplicações</t>
         </is>
       </c>
-      <c r="C24" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$25:$F$25,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="26" t="inlineStr">
+      <c r="C26" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>Convênio</t>
         </is>
       </c>
-      <c r="C25" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$F$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="26" t="inlineStr">
+      <c r="C27" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Faltas / atrasos</t>
         </is>
       </c>
-      <c r="C26" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="26" t="inlineStr">
+      <c r="C28" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Vale transporte 6%</t>
         </is>
       </c>
-      <c r="C27" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="26" t="inlineStr">
+      <c r="C29" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>INSS</t>
         </is>
       </c>
-      <c r="C28" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="26" t="inlineStr">
+      <c r="C30" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="C29" s="30">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="19" t="inlineStr">
+      <c r="C31" s="44">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$32:$F$32,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C30" s="38">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C32" s="50">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="45" t="inlineStr">
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/10/2026</t>
         </is>
       </c>
-      <c r="C32" s="46">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="47" t="inlineStr">
+      <c r="C34" s="58">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$35:$F$35,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Vendas do colaborador no mês (InovaFarma):</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Venda bruta</t>
         </is>
       </c>
-      <c r="C35" s="30">
+      <c r="C37" s="44">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Descontos concedidos</t>
         </is>
       </c>
-      <c r="C36" s="30">
+      <c r="C38" s="44">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>Venda líquida</t>
         </is>
       </c>
-      <c r="C37" s="30">
+      <c r="C39" s="44">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="26" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>Comissão apurada</t>
         </is>
       </c>
-      <c r="C38" s="30">
+      <c r="C40" s="44">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="26" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C39" s="30">
+      <c r="C41" s="44">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="35" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="47" t="inlineStr">
         <is>
           <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="35" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="47" t="inlineStr">
         <is>
           <t>Nesta loja a comissão paga é o DOBRO da apurada — por isso os dois valores são diferentes.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="35" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="47" t="inlineStr">
         <is>
           <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="35" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="47" t="inlineStr">
         <is>
           <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
         </is>
@@ -5869,7 +6912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5956,7 +6999,7 @@
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -5969,23 +7012,23 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A5,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="45" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="20">
         <f>ROUND(C5*F5,2)</f>
         <v/>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="H5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
         </is>
@@ -5997,7 +7040,7 @@
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Atestado médico (abonado)</t>
         </is>
@@ -6010,163 +7053,163 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="45" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="20">
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="43" t="inlineStr">
         <is>
           <t>Atestado médico de 02 a 08/09/2026, entregue em 02/09. Até 15 dias é abonado pela empresa: falta justificada, SEM desconto de salário nem de DSR. Anexar o atestado à pasta da funcionária.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="n"/>
-      <c r="B7" s="49" t="n"/>
-      <c r="C7" s="49" t="n"/>
-      <c r="D7" s="49" t="n"/>
-      <c r="E7" s="30">
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A7,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F7" s="31" t="n"/>
+      <c r="F7" s="26" t="n"/>
       <c r="G7" s="20">
         <f>ROUND(C7*F7,2)</f>
         <v/>
       </c>
-      <c r="H7" s="49" t="n"/>
-      <c r="I7" s="49" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="n"/>
-      <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="30">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A8,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="n"/>
+      <c r="F8" s="26" t="n"/>
       <c r="G8" s="20">
         <f>ROUND(C8*F8,2)</f>
         <v/>
       </c>
-      <c r="H8" s="49" t="n"/>
-      <c r="I8" s="49" t="n"/>
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="27" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="n"/>
-      <c r="B9" s="49" t="n"/>
-      <c r="C9" s="49" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="E9" s="30">
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A9,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F9" s="31" t="n"/>
+      <c r="F9" s="26" t="n"/>
       <c r="G9" s="20">
         <f>ROUND(C9*F9,2)</f>
         <v/>
       </c>
-      <c r="H9" s="49" t="n"/>
-      <c r="I9" s="49" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="27" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="30">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A10,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F10" s="31" t="n"/>
+      <c r="F10" s="26" t="n"/>
       <c r="G10" s="20">
         <f>ROUND(C10*F10,2)</f>
         <v/>
       </c>
-      <c r="H10" s="49" t="n"/>
-      <c r="I10" s="49" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="30">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A11,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F11" s="31" t="n"/>
+      <c r="F11" s="26" t="n"/>
       <c r="G11" s="20">
         <f>ROUND(C11*F11,2)</f>
         <v/>
       </c>
-      <c r="H11" s="49" t="n"/>
-      <c r="I11" s="49" t="n"/>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="30">
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A12,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F12" s="31" t="n"/>
+      <c r="F12" s="26" t="n"/>
       <c r="G12" s="20">
         <f>ROUND(C12*F12,2)</f>
         <v/>
       </c>
-      <c r="H12" s="49" t="n"/>
-      <c r="I12" s="49" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="30">
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A13,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F13" s="31" t="n"/>
+      <c r="F13" s="26" t="n"/>
       <c r="G13" s="20">
         <f>ROUND(C13*F13,2)</f>
         <v/>
       </c>
-      <c r="H13" s="49" t="n"/>
-      <c r="I13" s="49" t="n"/>
+      <c r="H13" s="27" t="n"/>
+      <c r="I13" s="27" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="30">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="44">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F14" s="31" t="n"/>
+      <c r="F14" s="26" t="n"/>
       <c r="G14" s="20">
         <f>ROUND(C14*F14,2)</f>
         <v/>
       </c>
-      <c r="H14" s="49" t="n"/>
-      <c r="I14" s="49" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n"/>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -2252,7 +2252,7 @@
         <v>12000</v>
       </c>
       <c r="D16" s="27" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E16" s="25">
         <f>ROUND(C16*IF(D16="",0,D16)/30,2)</f>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="T16" s="34" t="inlineStr">
         <is>
-          <t>Atestado de 02 a 08/09: 23 dias trabalhados. Ajustar se o atestado contar como dia trabalhado.</t>
+          <t>Atestado de 02 a 08/09 abonado: conta como dia trabalhado, meta cheia.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_TRANCOSO_pgto_05-10-2026.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'METAS SET.26'!$A$11:$T$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$138</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,6 +103,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
@@ -116,11 +121,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -238,10 +238,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -292,8 +292,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,26 +303,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="L11" s="29" t="inlineStr">
         <is>
-          <t>META 2 PROD. FOCO</t>
+          <t>META 2 (INCENTIVO INOVAFARMA)</t>
         </is>
       </c>
       <c r="M11" s="29" t="inlineStr">
@@ -2018,7 +2018,10 @@
         <f>IF(G12&gt;=1.2,J12,IF(G12&gt;=1,I12,IF(G12&gt;=0.8,H12,0)))</f>
         <v/>
       </c>
-      <c r="L12" s="26" t="n"/>
+      <c r="L12" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH(A12,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
+      </c>
       <c r="M12" s="26" t="n"/>
       <c r="N12" s="25" t="n"/>
       <c r="O12" s="32">
@@ -2035,11 +2038,11 @@
         <f>IF(AND(P12="SIM",$C$9="SIM"),IF(Q12="",0,Q12)+50,0)</f>
         <v/>
       </c>
-      <c r="S12" s="33">
+      <c r="S12" s="34">
         <f>ROUND(K12+IF(L12="",0,L12)+O12+R12,2)</f>
         <v/>
       </c>
-      <c r="T12" s="34" t="inlineStr">
+      <c r="T12" s="35" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09: sem dias trabalhados, fica fora da apuração.</t>
         </is>
@@ -2084,7 +2087,10 @@
         <f>IF(G13&gt;=1.2,J13,IF(G13&gt;=1,I13,IF(G13&gt;=0.8,H13,0)))</f>
         <v/>
       </c>
-      <c r="L13" s="26" t="n"/>
+      <c r="L13" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH(A13,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
+      </c>
       <c r="M13" s="26" t="n"/>
       <c r="N13" s="25" t="n">
         <v>940</v>
@@ -2103,11 +2109,11 @@
         <f>IF(AND(P13="SIM",$C$9="SIM"),IF(Q13="",0,Q13)+50,0)</f>
         <v/>
       </c>
-      <c r="S13" s="33">
+      <c r="S13" s="34">
         <f>ROUND(K13+IF(L13="",0,L13)+O13+R13,2)</f>
         <v/>
       </c>
-      <c r="T13" s="34" t="inlineStr">
+      <c r="T13" s="35" t="inlineStr">
         <is>
           <t>Farmacêutico: na Meta 3 vale a regra própria (equipe + 30%).</t>
         </is>
@@ -2152,7 +2158,10 @@
         <f>IF(G14&gt;=1.2,J14,IF(G14&gt;=1,I14,IF(G14&gt;=0.8,H14,0)))</f>
         <v/>
       </c>
-      <c r="L14" s="26" t="n"/>
+      <c r="L14" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH(A14,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
+      </c>
       <c r="M14" s="26" t="n"/>
       <c r="N14" s="25" t="n"/>
       <c r="O14" s="32">
@@ -2169,11 +2178,11 @@
         <f>IF(AND(P14="SIM",$C$9="SIM"),IF(Q14="",0,Q14)+50,0)</f>
         <v/>
       </c>
-      <c r="S14" s="33">
+      <c r="S14" s="34">
         <f>ROUND(K14+IF(L14="",0,L14)+O14+R14,2)</f>
         <v/>
       </c>
-      <c r="T14" s="34" t="inlineStr"/>
+      <c r="T14" s="35" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -2214,7 +2223,10 @@
         <f>IF(G15&gt;=1.2,J15,IF(G15&gt;=1,I15,IF(G15&gt;=0.8,H15,0)))</f>
         <v/>
       </c>
-      <c r="L15" s="26" t="n"/>
+      <c r="L15" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH(A15,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
+      </c>
       <c r="M15" s="26" t="n"/>
       <c r="N15" s="25" t="n"/>
       <c r="O15" s="32">
@@ -2231,11 +2243,11 @@
         <f>IF(AND(P15="SIM",$C$9="SIM"),IF(Q15="",0,Q15)+50,0)</f>
         <v/>
       </c>
-      <c r="S15" s="33">
+      <c r="S15" s="34">
         <f>ROUND(K15+IF(L15="",0,L15)+O15+R15,2)</f>
         <v/>
       </c>
-      <c r="T15" s="34" t="inlineStr"/>
+      <c r="T15" s="35" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -2276,7 +2288,10 @@
         <f>IF(G16&gt;=1.2,J16,IF(G16&gt;=1,I16,IF(G16&gt;=0.8,H16,0)))</f>
         <v/>
       </c>
-      <c r="L16" s="26" t="n"/>
+      <c r="L16" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH(A16,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
+      </c>
       <c r="M16" s="26" t="n"/>
       <c r="N16" s="25" t="n"/>
       <c r="O16" s="32">
@@ -2293,11 +2308,11 @@
         <f>IF(AND(P16="SIM",$C$9="SIM"),IF(Q16="",0,Q16)+50,0)</f>
         <v/>
       </c>
-      <c r="S16" s="33">
+      <c r="S16" s="34">
         <f>ROUND(K16+IF(L16="",0,L16)+O16+R16,2)</f>
         <v/>
       </c>
-      <c r="T16" s="34" t="inlineStr">
+      <c r="T16" s="35" t="inlineStr">
         <is>
           <t>Atestado de 02 a 08/09 abonado: conta como dia trabalhado, meta cheia.</t>
         </is>
@@ -2345,56 +2360,56 @@
       <c r="T17" s="18" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>COMO PREENCHER (células amarelas):</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="37" t="inlineStr">
         <is>
           <t>VENDA REALIZADA: total vendido no mês pelo código do vendedor (InovaFarma, venda líquida). DIAS TRAB.: dias efetivamente trabalhados — a meta cai na mesma proporção.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>META 1 — VOLUME: meta = média dos 3 últimos meses + 8%. 80% da meta paga o prêmio de 80%, 100% paga o de 100% e 120% paga o de 120%, conforme a faixa (A 150/250/500 · B 100/150/300 · C e D 50/80/150).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>META 2 — PRODUTOS FOCO: lançar o valor apurado na semana (vitaminas da campanha, packs, injetáveis, coquetel, brinco, kit ressaca). ATENÇÃO: se o incentivo já vier no relatório do InovaFarma (linhas INCENTIVO do holerite), não lançar de novo aqui.</t>
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>META 2 — PRODUTOS FOCO: é paga pelo campo de incentivo do InovaFarma (R$ 10 por item cadastrado no estoque). A coluna puxa o total de incentivos da aba BASE só para mostrar o ganho completo — no holerite ela entra pelas linhas INCENTIVO, e não numa linha de prêmio, para não pagar duas vezes.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>META 3 — PRÉ-VENCIDOS: escada mensal por vendedor (acima de R$ 1.000 = 100 · R$ 2.000 = 200 · R$ 3.000 = 300). Farmacêuticos têm regra própria: bateu a meta da coluna META PRÉ-V. FARMAC., recebe R$ 150.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>META 4 — PERFUMARIA 130%: meta da LOJA (bloco no topo). Se a loja bater 130% da média ou zerar o estoque, cada vendedora marcada recebe a comissão de perfumaria do mês mais R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Os prêmios entram sozinhos nas linhas PRÊMIO META 1 a 4 do holerite. Fonte: planilha Metas_Equipe_Set2026_v2.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>TRANCOSO: se ainda valer a redução combinada para compensar a comissão dobrada, ajustar o prêmio manualmente no holerite.</t>
         </is>
@@ -2429,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2457,42 +2472,42 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>MANOEL</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>INIURLE</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="G4" s="38" t="inlineStr">
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>ORIGEM / OBSERVAÇÃO</t>
         </is>
@@ -2504,68 +2519,68 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="B5" s="39" t="n"/>
-      <c r="C5" s="39" t="n"/>
-      <c r="D5" s="39" t="n"/>
-      <c r="E5" s="39" t="n"/>
-      <c r="F5" s="39" t="n"/>
-      <c r="G5" s="39" t="n"/>
-      <c r="H5" s="39" t="n"/>
+      <c r="B5" s="40" t="n"/>
+      <c r="C5" s="40" t="n"/>
+      <c r="D5" s="40" t="n"/>
+      <c r="E5" s="40" t="n"/>
+      <c r="F5" s="40" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="40" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="42" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="42" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="42" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="43">
         <f>SUM(B6:F6)</f>
         <v/>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H6" s="44" t="inlineStr">
         <is>
           <t>Piso 2026 R$ 1.621,00; gerente conforme ago/2026. CONFERIR admissões, afastamentos e férias do mês.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
@@ -2573,35 +2588,35 @@
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="43" t="inlineStr">
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="33">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
@@ -2609,34 +2624,34 @@
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="33">
         <f>ROUND('BASE INOVAFARMA SET.26'!F6*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="33">
         <f>ROUND('BASE INOVAFARMA SET.26'!F7*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="33">
         <f>ROUND('BASE INOVAFARMA SET.26'!F8*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="33">
         <f>ROUND('BASE INOVAFARMA SET.26'!F9*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
@@ -2644,14 +2659,14 @@
         <f>SUM(B9:F9)</f>
         <v/>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>Apurado no InovaFarma (aba BASE INOVAFARMA SET.26), JÁ MULTIPLICADO POR 2 (multiplicador na aba PARÂMETROS). UILLIAN não recebe(m) comissão — lançado zero.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
@@ -2665,7 +2680,7 @@
         <f>SUM(B10:F10)</f>
         <v/>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>PREENCHER: PDV antigos e complementos de comissão acordados, se houver.</t>
         </is>
@@ -2701,14 +2716,14 @@
         <f>SUM(B11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="43" t="inlineStr">
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>Base do DSR junto com as horas extras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
@@ -2737,14 +2752,14 @@
         <f>SUM(B12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H12" s="44" t="inlineStr">
         <is>
           <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
@@ -2758,14 +2773,14 @@
         <f>SUM(B13:F13)</f>
         <v/>
       </c>
-      <c r="H13" s="43" t="inlineStr">
+      <c r="H13" s="44" t="inlineStr">
         <is>
           <t>Conforme acordo da loja.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
@@ -2779,35 +2794,35 @@
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="inlineStr">
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>Conforme apuração do caixa.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="33">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="33">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="33">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="33">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="33">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
@@ -2815,124 +2830,109 @@
         <f>SUM(B15:F15)</f>
         <v/>
       </c>
-      <c r="H15" s="43" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>Da aba METAS SET.26: venda do mês contra a meta individual (80% / 100% / 120%). Aplicar a redução combinada pela comissão dobrada, se ainda valer.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="B16" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="B16" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
       <c r="G16" s="20">
         <f>SUM(B16:F16)</f>
         <v/>
       </c>
-      <c r="H16" s="43" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: vitaminas, packs, injetáveis, coquetel, brinco e kit ressaca.</t>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="B17" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="B17" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="33">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
         <v/>
       </c>
       <c r="G17" s="20">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="43" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
-        </is>
-      </c>
-      <c r="B18" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(B$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(C$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(D$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(E$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$16,MATCH(F$4,'METAS SET.26'!$A$12:$A$16,0)),0)</f>
-        <v/>
-      </c>
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
       <c r="G18" s="20">
         <f>SUM(B18:F18)</f>
         <v/>
       </c>
-      <c r="H18" s="43" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>PREENCHER se houve férias no mês; informar o período.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t>FÉRIAS (DIAS GOZADOS)</t>
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
       <c r="B19" s="26" t="n"/>
@@ -2944,252 +2944,252 @@
         <f>SUM(B19:F19)</f>
         <v/>
       </c>
-      <c r="H19" s="43" t="inlineStr">
-        <is>
-          <t>PREENCHER se houve férias no mês; informar o período.</t>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="B20" s="33">
+        <f>'BASE INOVAFARMA SET.26'!G5</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>'BASE INOVAFARMA SET.26'!G6</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>'BASE INOVAFARMA SET.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>'BASE INOVAFARMA SET.26'!G8</f>
+        <v/>
+      </c>
+      <c r="F20" s="33">
+        <f>'BASE INOVAFARMA SET.26'!G9</f>
+        <v/>
+      </c>
       <c r="G20" s="20">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
-      <c r="H20" s="43" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+      <c r="H20" s="44" t="inlineStr">
+        <is>
+          <t>Incentivo de injetáveis apurado no InovaFarma. As linhas de incentivo incluem a META 2 (produtos foco) do programa de metas. Incentivo é simples: NÃO entra em dobro.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="B21" s="44">
-        <f>'BASE INOVAFARMA SET.26'!G5</f>
-        <v/>
-      </c>
-      <c r="C21" s="44">
-        <f>'BASE INOVAFARMA SET.26'!G6</f>
-        <v/>
-      </c>
-      <c r="D21" s="44">
-        <f>'BASE INOVAFARMA SET.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E21" s="44">
-        <f>'BASE INOVAFARMA SET.26'!G8</f>
-        <v/>
-      </c>
-      <c r="F21" s="44">
-        <f>'BASE INOVAFARMA SET.26'!G9</f>
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>'BASE INOVAFARMA SET.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C21" s="33">
+        <f>'BASE INOVAFARMA SET.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D21" s="33">
+        <f>'BASE INOVAFARMA SET.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E21" s="33">
+        <f>'BASE INOVAFARMA SET.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F21" s="33">
+        <f>'BASE INOVAFARMA SET.26'!H9</f>
         <v/>
       </c>
       <c r="G21" s="20">
         <f>SUM(B21:F21)</f>
         <v/>
       </c>
-      <c r="H21" s="43" t="inlineStr">
-        <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma. Incentivo é simples: NÃO entra em dobro.</t>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B22" s="44">
-        <f>'BASE INOVAFARMA SET.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C22" s="44">
-        <f>'BASE INOVAFARMA SET.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D22" s="44">
-        <f>'BASE INOVAFARMA SET.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E22" s="44">
-        <f>'BASE INOVAFARMA SET.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F22" s="44">
-        <f>'BASE INOVAFARMA SET.26'!H9</f>
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>'BASE INOVAFARMA SET.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C22" s="33">
+        <f>'BASE INOVAFARMA SET.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>'BASE INOVAFARMA SET.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
+        <f>'BASE INOVAFARMA SET.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F22" s="33">
+        <f>'BASE INOVAFARMA SET.26'!I9</f>
         <v/>
       </c>
       <c r="G22" s="20">
         <f>SUM(B22:F22)</f>
         <v/>
       </c>
-      <c r="H22" s="43" t="inlineStr">
-        <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>Populares, oficinais e similar normal.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B23" s="44">
-        <f>'BASE INOVAFARMA SET.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C23" s="44">
-        <f>'BASE INOVAFARMA SET.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D23" s="44">
-        <f>'BASE INOVAFARMA SET.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E23" s="44">
-        <f>'BASE INOVAFARMA SET.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F23" s="44">
-        <f>'BASE INOVAFARMA SET.26'!I9</f>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B23" s="20">
+        <f>SUM(B6:B22)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>SUM(C6:C22)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>SUM(D6:D22)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f>SUM(E6:E22)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f>SUM(F6:F22)-F9-F10</f>
         <v/>
       </c>
       <c r="G23" s="20">
         <f>SUM(B23:F23)</f>
         <v/>
       </c>
-      <c r="H23" s="43" t="inlineStr">
-        <is>
-          <t>Populares, oficinais e similar normal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B24" s="20">
-        <f>SUM(B6:B23)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C24" s="20">
-        <f>SUM(C6:C23)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f>SUM(D6:D23)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f>SUM(E6:E23)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>SUM(F6:F23)-F9-F10</f>
-        <v/>
-      </c>
-      <c r="G24" s="20">
-        <f>SUM(B24:F24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="43" t="inlineStr">
+      <c r="H23" s="44" t="inlineStr">
         <is>
           <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS  (lançar com sinal negativo)</t>
         </is>
       </c>
-      <c r="B25" s="39" t="n"/>
-      <c r="C25" s="39" t="n"/>
-      <c r="D25" s="39" t="n"/>
-      <c r="E25" s="39" t="n"/>
-      <c r="F25" s="39" t="n"/>
-      <c r="G25" s="39" t="n"/>
-      <c r="H25" s="39" t="n"/>
+      <c r="B24" s="40" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="20">
+        <f>SUM(B25:F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREENCHER com os vales adiantados durante setembro. </t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="20">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B26" s="46">
+        <f>-(B20+B21+B22)</f>
+        <v/>
+      </c>
+      <c r="C26" s="46">
+        <f>-(C20+C21+C22)</f>
+        <v/>
+      </c>
+      <c r="D26" s="46">
+        <f>-(D20+D21+D22)</f>
+        <v/>
+      </c>
+      <c r="E26" s="46">
+        <f>-(E20+E21+E22)</f>
+        <v/>
+      </c>
+      <c r="F26" s="46">
+        <f>-(F20+F21+F22)</f>
+        <v/>
+      </c>
+      <c r="G26" s="43">
         <f>SUM(B26:F26)</f>
         <v/>
       </c>
-      <c r="H26" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PREENCHER com os vales adiantados durante setembro. </t>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="40" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B27" s="46">
-        <f>-(B21+B22+B23)</f>
-        <v/>
-      </c>
-      <c r="C27" s="46">
-        <f>-(C21+C22+C23)</f>
-        <v/>
-      </c>
-      <c r="D27" s="46">
-        <f>-(D21+D22+D23)</f>
-        <v/>
-      </c>
-      <c r="E27" s="46">
-        <f>-(E21+E22+E23)</f>
-        <v/>
-      </c>
-      <c r="F27" s="46">
-        <f>-(F21+F22+F23)</f>
-        <v/>
-      </c>
-      <c r="G27" s="42">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="20">
         <f>SUM(B27:F27)</f>
         <v/>
       </c>
-      <c r="H27" s="43" t="inlineStr">
-        <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o convênio de setembro.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
       <c r="B28" s="26" t="n"/>
@@ -3201,58 +3201,58 @@
         <f>SUM(B28:F28)</f>
         <v/>
       </c>
-      <c r="H28" s="43" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o convênio de setembro.</t>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO FALTAS / ATRASOS</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="20">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="43">
         <f>SUM(B29:F29)</f>
         <v/>
       </c>
-      <c r="H29" s="43" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o ponto.</t>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B30" s="41" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="42">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="20">
         <f>SUM(B30:F30)</f>
         <v/>
       </c>
-      <c r="H30" s="43" t="inlineStr">
-        <is>
-          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
         </is>
       </c>
       <c r="B31" s="26" t="n"/>
@@ -3264,133 +3264,133 @@
         <f>SUM(B31:F31)</f>
         <v/>
       </c>
-      <c r="H31" s="43" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="B32" s="20">
+        <f>SUM(B25:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f>SUM(C25:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f>SUM(D25:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="20">
+        <f>SUM(E25:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
+        <f>SUM(F25:F31)</f>
+        <v/>
+      </c>
       <c r="G32" s="20">
         <f>SUM(B32:F32)</f>
         <v/>
       </c>
-      <c r="H32" s="43" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="B33" s="20">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="20">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="20">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="20">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="20">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="20">
-        <f>SUM(B33:F33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="43" t="inlineStr"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="H32" s="44" t="inlineStr"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="B34" s="39" t="n"/>
-      <c r="C34" s="39" t="n"/>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="39" t="n"/>
-      <c r="F34" s="39" t="n"/>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="39" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="40" t="n"/>
+      <c r="D33" s="40" t="n"/>
+      <c r="E33" s="40" t="n"/>
+      <c r="F33" s="40" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="40" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER (05/10/2026)</t>
         </is>
       </c>
-      <c r="B35" s="33">
-        <f>B24+B33</f>
-        <v/>
-      </c>
-      <c r="C35" s="33">
-        <f>C24+C33</f>
-        <v/>
-      </c>
-      <c r="D35" s="33">
-        <f>D24+D33</f>
-        <v/>
-      </c>
-      <c r="E35" s="33">
-        <f>E24+E33</f>
-        <v/>
-      </c>
-      <c r="F35" s="33">
-        <f>F24+F33</f>
-        <v/>
-      </c>
-      <c r="G35" s="33">
-        <f>SUM(B35:F35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="43" t="inlineStr">
+      <c r="B34" s="34">
+        <f>B23+B32</f>
+        <v/>
+      </c>
+      <c r="C34" s="34">
+        <f>C23+C32</f>
+        <v/>
+      </c>
+      <c r="D34" s="34">
+        <f>D23+D32</f>
+        <v/>
+      </c>
+      <c r="E34" s="34">
+        <f>E23+E32</f>
+        <v/>
+      </c>
+      <c r="F34" s="34">
+        <f>F23+F32</f>
+        <v/>
+      </c>
+      <c r="G34" s="34">
+        <f>SUM(B34:F34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="44" t="inlineStr">
         <is>
           <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
-      <c r="B36" s="39" t="n"/>
-      <c r="C36" s="39" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="39" t="n"/>
-      <c r="F36" s="39" t="n"/>
-      <c r="G36" s="39" t="n"/>
-      <c r="H36" s="39" t="n"/>
+      <c r="B35" s="40" t="n"/>
+      <c r="C35" s="40" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="40" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>VALE TRANSPORTE (compra out/26)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="20">
+        <f>SUM(B36:F36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PREENCHER com as passagens compradas. </t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>VALE TRANSPORTE (compra out/26)</t>
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
       <c r="B37" s="26" t="n"/>
@@ -3402,120 +3402,99 @@
         <f>SUM(B37:F37)</f>
         <v/>
       </c>
-      <c r="H37" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PREENCHER com as passagens compradas. </t>
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme escala de domingos e feriados.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="20">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="43">
         <f>SUM(B38:F38)</f>
         <v/>
       </c>
-      <c r="H38" s="43" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme escala de domingos e feriados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="40" t="inlineStr">
-        <is>
-          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
-        </is>
-      </c>
-      <c r="B39" s="41" t="n"/>
-      <c r="C39" s="41" t="n"/>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="41" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="42">
-        <f>SUM(B39:F39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="43" t="inlineStr">
+      <c r="H38" s="44" t="inlineStr">
         <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. VALDICK: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B40" s="47" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B41" s="47" t="inlineStr"/>
+          <t>Célula amarela, texto azul</t>
+        </is>
+      </c>
+      <c r="B41" s="47" t="inlineStr">
+        <is>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Texto verde</t>
         </is>
       </c>
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Texto preto em célula verde</t>
         </is>
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="21" t="inlineStr">
-        <is>
-          <t>Texto preto em célula verde</t>
-        </is>
-      </c>
-      <c r="B45" s="47" t="inlineStr">
-        <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H39"/>
+  <autoFilter ref="A4:H38"/>
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B44:H44"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3527,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3552,2894 +3531,2784 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D5" s="44">
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D5" s="33">
         <f>'HOLERITE SET.26'!B6</f>
         <v/>
       </c>
       <c r="E5" s="48" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D6" s="44">
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D6" s="33">
         <f>'HOLERITE SET.26'!B7</f>
         <v/>
       </c>
       <c r="E6" s="48" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D7" s="44">
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D7" s="33">
         <f>'HOLERITE SET.26'!B8</f>
         <v/>
       </c>
       <c r="E7" s="48" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D8" s="44">
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D8" s="33">
         <f>'HOLERITE SET.26'!B11</f>
         <v/>
       </c>
       <c r="E8" s="48" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D9" s="44">
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D9" s="33">
         <f>'HOLERITE SET.26'!B12</f>
         <v/>
       </c>
       <c r="E9" s="48" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D10" s="44">
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D10" s="33">
         <f>'HOLERITE SET.26'!B13</f>
         <v/>
       </c>
       <c r="E10" s="48" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D11" s="44">
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D11" s="33">
         <f>'HOLERITE SET.26'!B14</f>
         <v/>
       </c>
       <c r="E11" s="48" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D12" s="44">
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D12" s="33">
         <f>'HOLERITE SET.26'!B15</f>
         <v/>
       </c>
       <c r="E12" s="48" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D13" s="44">
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D13" s="33">
         <f>'HOLERITE SET.26'!B16</f>
         <v/>
       </c>
       <c r="E13" s="48" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>UILLIAN</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D14" s="33">
+        <f>'HOLERITE SET.26'!B17</f>
+        <v/>
+      </c>
+      <c r="E14" s="48" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>FÉRIAS</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D15" s="33">
+        <f>'HOLERITE SET.26'!B18</f>
+        <v/>
+      </c>
+      <c r="E15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D16" s="33">
+        <f>'HOLERITE SET.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E16" s="48" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D17" s="33">
+        <f>'HOLERITE SET.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E17" s="48" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D18" s="33">
+        <f>'HOLERITE SET.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E18" s="48" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D19" s="33">
+        <f>'HOLERITE SET.26'!B22</f>
+        <v/>
+      </c>
+      <c r="E19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="D20" s="50">
+        <f>'HOLERITE SET.26'!B23</f>
+        <v/>
+      </c>
+      <c r="E20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D21" s="33">
+        <f>'HOLERITE SET.26'!B25</f>
+        <v/>
+      </c>
+      <c r="E21" s="48" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D22" s="33">
+        <f>'HOLERITE SET.26'!B26</f>
+        <v/>
+      </c>
+      <c r="E22" s="48" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D23" s="33">
+        <f>'HOLERITE SET.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E23" s="48" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO FALTAS / ATRASOS</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D24" s="33">
+        <f>'HOLERITE SET.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E24" s="48" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D25" s="33">
+        <f>'HOLERITE SET.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E25" s="48" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D26" s="33">
+        <f>'HOLERITE SET.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E26" s="48" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D27" s="33">
+        <f>'HOLERITE SET.26'!B31</f>
+        <v/>
+      </c>
+      <c r="E27" s="48" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="D28" s="50">
+        <f>'HOLERITE SET.26'!B32</f>
+        <v/>
+      </c>
+      <c r="E28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>UILLIAN</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER</t>
+        </is>
+      </c>
+      <c r="C29" s="52" t="inlineStr">
+        <is>
+          <t>Líquido</t>
+        </is>
+      </c>
+      <c r="D29" s="53">
+        <f>'HOLERITE SET.26'!B34</f>
+        <v/>
+      </c>
+      <c r="E29" s="54" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>SALÁRIO BASE</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D31" s="33">
+        <f>'HOLERITE SET.26'!C6</f>
+        <v/>
+      </c>
+      <c r="E31" s="48" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D32" s="33">
+        <f>'HOLERITE SET.26'!C7</f>
+        <v/>
+      </c>
+      <c r="E32" s="48" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D33" s="33">
+        <f>'HOLERITE SET.26'!C8</f>
+        <v/>
+      </c>
+      <c r="E33" s="48" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>COMISSÃO SOBRE VENDAS</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D34" s="33">
+        <f>'HOLERITE SET.26'!C11</f>
+        <v/>
+      </c>
+      <c r="E34" s="48" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>REPOUSO REMUNERADO / DSR</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D35" s="33">
+        <f>'HOLERITE SET.26'!C12</f>
+        <v/>
+      </c>
+      <c r="E35" s="48" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>AUXÍLIO GERÊNCIA</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D36" s="33">
+        <f>'HOLERITE SET.26'!C13</f>
+        <v/>
+      </c>
+      <c r="E36" s="48" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>ADICIONAL PRÊMIO META CAIXA</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D37" s="33">
+        <f>'HOLERITE SET.26'!C14</f>
+        <v/>
+      </c>
+      <c r="E37" s="48" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D38" s="33">
+        <f>'HOLERITE SET.26'!C15</f>
+        <v/>
+      </c>
+      <c r="E38" s="48" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C14" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D14" s="44">
-        <f>'HOLERITE SET.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="48" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D39" s="33">
+        <f>'HOLERITE SET.26'!C16</f>
+        <v/>
+      </c>
+      <c r="E39" s="48" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D15" s="44">
-        <f>'HOLERITE SET.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="48" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D40" s="33">
+        <f>'HOLERITE SET.26'!C17</f>
+        <v/>
+      </c>
+      <c r="E40" s="48" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D16" s="44">
-        <f>'HOLERITE SET.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="48" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D41" s="33">
+        <f>'HOLERITE SET.26'!C18</f>
+        <v/>
+      </c>
+      <c r="E41" s="48" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D17" s="44">
-        <f>'HOLERITE SET.26'!B20</f>
-        <v/>
-      </c>
-      <c r="E17" s="48" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D42" s="33">
+        <f>'HOLERITE SET.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E42" s="48" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D18" s="44">
-        <f>'HOLERITE SET.26'!B21</f>
-        <v/>
-      </c>
-      <c r="E18" s="48" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D43" s="33">
+        <f>'HOLERITE SET.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E43" s="48" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D19" s="44">
-        <f>'HOLERITE SET.26'!B22</f>
-        <v/>
-      </c>
-      <c r="E19" s="48" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D44" s="33">
+        <f>'HOLERITE SET.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E44" s="48" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C20" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D20" s="44">
-        <f>'HOLERITE SET.26'!B23</f>
-        <v/>
-      </c>
-      <c r="E20" s="48" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="49" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B21" s="49" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D45" s="33">
+        <f>'HOLERITE SET.26'!C22</f>
+        <v/>
+      </c>
+      <c r="E45" s="48" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="49" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C46" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D21" s="50">
-        <f>'HOLERITE SET.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E21" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B22" s="40" t="inlineStr">
+      <c r="D46" s="50">
+        <f>'HOLERITE SET.26'!C23</f>
+        <v/>
+      </c>
+      <c r="E46" s="18" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C22" s="40" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="44">
-        <f>'HOLERITE SET.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="48" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="D47" s="33">
+        <f>'HOLERITE SET.26'!C25</f>
+        <v/>
+      </c>
+      <c r="E47" s="48" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="44">
-        <f>'HOLERITE SET.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="48" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B24" s="40" t="inlineStr">
+      <c r="D48" s="33">
+        <f>'HOLERITE SET.26'!C26</f>
+        <v/>
+      </c>
+      <c r="E48" s="48" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C24" s="40" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="44">
-        <f>'HOLERITE SET.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="48" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="D49" s="33">
+        <f>'HOLERITE SET.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E49" s="48" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C50" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D25" s="44">
-        <f>'HOLERITE SET.26'!B29</f>
-        <v/>
-      </c>
-      <c r="E25" s="48" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B26" s="40" t="inlineStr">
+      <c r="D50" s="33">
+        <f>'HOLERITE SET.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E50" s="48" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C26" s="40" t="inlineStr">
+      <c r="C51" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D26" s="44">
-        <f>'HOLERITE SET.26'!B30</f>
-        <v/>
-      </c>
-      <c r="E26" s="48" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="D51" s="33">
+        <f>'HOLERITE SET.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E51" s="48" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D27" s="44">
-        <f>'HOLERITE SET.26'!B31</f>
-        <v/>
-      </c>
-      <c r="E27" s="48" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B28" s="40" t="inlineStr">
+      <c r="D52" s="33">
+        <f>'HOLERITE SET.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E52" s="48" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C28" s="40" t="inlineStr">
+      <c r="C53" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D28" s="44">
-        <f>'HOLERITE SET.26'!B32</f>
-        <v/>
-      </c>
-      <c r="E28" s="48" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="49" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="D53" s="33">
+        <f>'HOLERITE SET.26'!C31</f>
+        <v/>
+      </c>
+      <c r="E53" s="48" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="49" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B54" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C29" s="49" t="inlineStr">
+      <c r="C54" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D29" s="50">
-        <f>'HOLERITE SET.26'!B33</f>
-        <v/>
-      </c>
-      <c r="E29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="51" t="inlineStr">
-        <is>
-          <t>UILLIAN</t>
-        </is>
-      </c>
-      <c r="B30" s="52" t="inlineStr">
+      <c r="D54" s="50">
+        <f>'HOLERITE SET.26'!C32</f>
+        <v/>
+      </c>
+      <c r="E54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="51" t="inlineStr">
+        <is>
+          <t>MANOEL</t>
+        </is>
+      </c>
+      <c r="B55" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C30" s="52" t="inlineStr">
+      <c r="C55" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D30" s="53">
-        <f>'HOLERITE SET.26'!B35</f>
-        <v/>
-      </c>
-      <c r="E30" s="54" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="D55" s="53">
+        <f>'HOLERITE SET.26'!C34</f>
+        <v/>
+      </c>
+      <c r="E55" s="54" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D32" s="44">
-        <f>'HOLERITE SET.26'!C6</f>
-        <v/>
-      </c>
-      <c r="E32" s="48" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D57" s="33">
+        <f>'HOLERITE SET.26'!D6</f>
+        <v/>
+      </c>
+      <c r="E57" s="48" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D33" s="44">
-        <f>'HOLERITE SET.26'!C7</f>
-        <v/>
-      </c>
-      <c r="E33" s="48" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D58" s="33">
+        <f>'HOLERITE SET.26'!D7</f>
+        <v/>
+      </c>
+      <c r="E58" s="48" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B59" s="41" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D34" s="44">
-        <f>'HOLERITE SET.26'!C8</f>
-        <v/>
-      </c>
-      <c r="E34" s="48" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D59" s="33">
+        <f>'HOLERITE SET.26'!D8</f>
+        <v/>
+      </c>
+      <c r="E59" s="48" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B60" s="41" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D35" s="44">
-        <f>'HOLERITE SET.26'!C11</f>
-        <v/>
-      </c>
-      <c r="E35" s="48" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D60" s="33">
+        <f>'HOLERITE SET.26'!D11</f>
+        <v/>
+      </c>
+      <c r="E60" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B61" s="41" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D36" s="44">
-        <f>'HOLERITE SET.26'!C12</f>
-        <v/>
-      </c>
-      <c r="E36" s="48" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D61" s="33">
+        <f>'HOLERITE SET.26'!D12</f>
+        <v/>
+      </c>
+      <c r="E61" s="48" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B62" s="41" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D37" s="44">
-        <f>'HOLERITE SET.26'!C13</f>
-        <v/>
-      </c>
-      <c r="E37" s="48" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D62" s="33">
+        <f>'HOLERITE SET.26'!D13</f>
+        <v/>
+      </c>
+      <c r="E62" s="48" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B63" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D38" s="44">
-        <f>'HOLERITE SET.26'!C14</f>
-        <v/>
-      </c>
-      <c r="E38" s="48" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D63" s="33">
+        <f>'HOLERITE SET.26'!D14</f>
+        <v/>
+      </c>
+      <c r="E63" s="48" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B64" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D39" s="44">
-        <f>'HOLERITE SET.26'!C15</f>
-        <v/>
-      </c>
-      <c r="E39" s="48" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D40" s="44">
-        <f>'HOLERITE SET.26'!C16</f>
-        <v/>
-      </c>
-      <c r="E40" s="48" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B41" s="40" t="inlineStr">
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D64" s="33">
+        <f>'HOLERITE SET.26'!D15</f>
+        <v/>
+      </c>
+      <c r="E64" s="48" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D41" s="44">
-        <f>'HOLERITE SET.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E41" s="48" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B42" s="40" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D65" s="33">
+        <f>'HOLERITE SET.26'!D16</f>
+        <v/>
+      </c>
+      <c r="E65" s="48" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C42" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D42" s="44">
-        <f>'HOLERITE SET.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E42" s="48" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D66" s="33">
+        <f>'HOLERITE SET.26'!D17</f>
+        <v/>
+      </c>
+      <c r="E66" s="48" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D43" s="44">
-        <f>'HOLERITE SET.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E43" s="48" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D67" s="33">
+        <f>'HOLERITE SET.26'!D18</f>
+        <v/>
+      </c>
+      <c r="E67" s="48" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C44" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D44" s="44">
-        <f>'HOLERITE SET.26'!C20</f>
-        <v/>
-      </c>
-      <c r="E44" s="48" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B45" s="40" t="inlineStr">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D68" s="33">
+        <f>'HOLERITE SET.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E68" s="48" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B69" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D45" s="44">
-        <f>'HOLERITE SET.26'!C21</f>
-        <v/>
-      </c>
-      <c r="E45" s="48" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B46" s="40" t="inlineStr">
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D69" s="33">
+        <f>'HOLERITE SET.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E69" s="48" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B70" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D46" s="44">
-        <f>'HOLERITE SET.26'!C22</f>
-        <v/>
-      </c>
-      <c r="E46" s="48" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B47" s="40" t="inlineStr">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D70" s="33">
+        <f>'HOLERITE SET.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E70" s="48" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D47" s="44">
-        <f>'HOLERITE SET.26'!C23</f>
-        <v/>
-      </c>
-      <c r="E47" s="48" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="49" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B48" s="49" t="inlineStr">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D71" s="33">
+        <f>'HOLERITE SET.26'!D22</f>
+        <v/>
+      </c>
+      <c r="E71" s="48" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="49" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B72" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C48" s="49" t="inlineStr">
+      <c r="C72" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D48" s="50">
-        <f>'HOLERITE SET.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E48" s="18" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B49" s="40" t="inlineStr">
+      <c r="D72" s="50">
+        <f>'HOLERITE SET.26'!D23</f>
+        <v/>
+      </c>
+      <c r="E72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B73" s="41" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D49" s="44">
-        <f>'HOLERITE SET.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E49" s="48" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="D73" s="33">
+        <f>'HOLERITE SET.26'!D25</f>
+        <v/>
+      </c>
+      <c r="E73" s="48" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D50" s="44">
-        <f>'HOLERITE SET.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E50" s="48" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B51" s="40" t="inlineStr">
+      <c r="D74" s="33">
+        <f>'HOLERITE SET.26'!D26</f>
+        <v/>
+      </c>
+      <c r="E74" s="48" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B75" s="41" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D51" s="44">
-        <f>'HOLERITE SET.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E51" s="48" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B52" s="40" t="inlineStr">
+      <c r="D75" s="33">
+        <f>'HOLERITE SET.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E75" s="48" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B76" s="41" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D52" s="44">
-        <f>'HOLERITE SET.26'!C29</f>
-        <v/>
-      </c>
-      <c r="E52" s="48" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B53" s="40" t="inlineStr">
+      <c r="D76" s="33">
+        <f>'HOLERITE SET.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E76" s="48" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B77" s="41" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C53" s="40" t="inlineStr">
+      <c r="C77" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D53" s="44">
-        <f>'HOLERITE SET.26'!C30</f>
-        <v/>
-      </c>
-      <c r="E53" s="48" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B54" s="40" t="inlineStr">
+      <c r="D77" s="33">
+        <f>'HOLERITE SET.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E77" s="48" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B78" s="41" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D54" s="44">
-        <f>'HOLERITE SET.26'!C31</f>
-        <v/>
-      </c>
-      <c r="E54" s="48" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="40" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="inlineStr">
+      <c r="D78" s="33">
+        <f>'HOLERITE SET.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E78" s="48" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="41" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B79" s="41" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C55" s="40" t="inlineStr">
+      <c r="C79" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D55" s="44">
-        <f>'HOLERITE SET.26'!C32</f>
-        <v/>
-      </c>
-      <c r="E55" s="48" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="49" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B56" s="49" t="inlineStr">
+      <c r="D79" s="33">
+        <f>'HOLERITE SET.26'!D31</f>
+        <v/>
+      </c>
+      <c r="E79" s="48" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="49" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B80" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C56" s="49" t="inlineStr">
+      <c r="C80" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D56" s="50">
-        <f>'HOLERITE SET.26'!C33</f>
-        <v/>
-      </c>
-      <c r="E56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="51" t="inlineStr">
-        <is>
-          <t>MANOEL</t>
-        </is>
-      </c>
-      <c r="B57" s="52" t="inlineStr">
+      <c r="D80" s="50">
+        <f>'HOLERITE SET.26'!D32</f>
+        <v/>
+      </c>
+      <c r="E80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="51" t="inlineStr">
+        <is>
+          <t>VALDICK</t>
+        </is>
+      </c>
+      <c r="B81" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C57" s="52" t="inlineStr">
+      <c r="C81" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D57" s="53">
-        <f>'HOLERITE SET.26'!C35</f>
-        <v/>
-      </c>
-      <c r="E57" s="54" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B59" s="40" t="inlineStr">
+      <c r="D81" s="53">
+        <f>'HOLERITE SET.26'!D34</f>
+        <v/>
+      </c>
+      <c r="E81" s="54" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D59" s="44">
-        <f>'HOLERITE SET.26'!D6</f>
-        <v/>
-      </c>
-      <c r="E59" s="48" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B60" s="40" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D83" s="33">
+        <f>'HOLERITE SET.26'!E6</f>
+        <v/>
+      </c>
+      <c r="E83" s="48" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C60" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D60" s="44">
-        <f>'HOLERITE SET.26'!D7</f>
-        <v/>
-      </c>
-      <c r="E60" s="48" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B61" s="40" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D84" s="33">
+        <f>'HOLERITE SET.26'!E7</f>
+        <v/>
+      </c>
+      <c r="E84" s="48" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D61" s="44">
-        <f>'HOLERITE SET.26'!D8</f>
-        <v/>
-      </c>
-      <c r="E61" s="48" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B62" s="40" t="inlineStr">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D85" s="33">
+        <f>'HOLERITE SET.26'!E8</f>
+        <v/>
+      </c>
+      <c r="E85" s="48" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B86" s="41" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C62" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D62" s="44">
-        <f>'HOLERITE SET.26'!D11</f>
-        <v/>
-      </c>
-      <c r="E62" s="48" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B63" s="40" t="inlineStr">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D86" s="33">
+        <f>'HOLERITE SET.26'!E11</f>
+        <v/>
+      </c>
+      <c r="E86" s="48" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B87" s="41" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D63" s="44">
-        <f>'HOLERITE SET.26'!D12</f>
-        <v/>
-      </c>
-      <c r="E63" s="48" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B64" s="40" t="inlineStr">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D87" s="33">
+        <f>'HOLERITE SET.26'!E12</f>
+        <v/>
+      </c>
+      <c r="E87" s="48" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B88" s="41" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C64" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D64" s="44">
-        <f>'HOLERITE SET.26'!D13</f>
-        <v/>
-      </c>
-      <c r="E64" s="48" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B65" s="40" t="inlineStr">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D88" s="33">
+        <f>'HOLERITE SET.26'!E13</f>
+        <v/>
+      </c>
+      <c r="E88" s="48" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B89" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C65" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D65" s="44">
-        <f>'HOLERITE SET.26'!D14</f>
-        <v/>
-      </c>
-      <c r="E65" s="48" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B66" s="40" t="inlineStr">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D89" s="33">
+        <f>'HOLERITE SET.26'!E14</f>
+        <v/>
+      </c>
+      <c r="E89" s="48" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B90" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C66" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D66" s="44">
-        <f>'HOLERITE SET.26'!D15</f>
-        <v/>
-      </c>
-      <c r="E66" s="48" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B67" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C67" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D67" s="44">
-        <f>'HOLERITE SET.26'!D16</f>
-        <v/>
-      </c>
-      <c r="E67" s="48" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B68" s="40" t="inlineStr">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D90" s="33">
+        <f>'HOLERITE SET.26'!E15</f>
+        <v/>
+      </c>
+      <c r="E90" s="48" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B91" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C68" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D68" s="44">
-        <f>'HOLERITE SET.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E68" s="48" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B69" s="40" t="inlineStr">
+      <c r="C91" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D91" s="33">
+        <f>'HOLERITE SET.26'!E16</f>
+        <v/>
+      </c>
+      <c r="E91" s="48" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B92" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C69" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D69" s="44">
-        <f>'HOLERITE SET.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E69" s="48" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B70" s="40" t="inlineStr">
+      <c r="C92" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D92" s="33">
+        <f>'HOLERITE SET.26'!E17</f>
+        <v/>
+      </c>
+      <c r="E92" s="48" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B93" s="41" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C70" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D70" s="44">
-        <f>'HOLERITE SET.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E70" s="48" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B71" s="40" t="inlineStr">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D93" s="33">
+        <f>'HOLERITE SET.26'!E18</f>
+        <v/>
+      </c>
+      <c r="E93" s="48" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B94" s="41" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C71" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D71" s="44">
-        <f>'HOLERITE SET.26'!D20</f>
-        <v/>
-      </c>
-      <c r="E71" s="48" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B72" s="40" t="inlineStr">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D94" s="33">
+        <f>'HOLERITE SET.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E94" s="48" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B95" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C72" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D72" s="44">
-        <f>'HOLERITE SET.26'!D21</f>
-        <v/>
-      </c>
-      <c r="E72" s="48" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B73" s="40" t="inlineStr">
+      <c r="C95" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D95" s="33">
+        <f>'HOLERITE SET.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E95" s="48" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B96" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C73" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D73" s="44">
-        <f>'HOLERITE SET.26'!D22</f>
-        <v/>
-      </c>
-      <c r="E73" s="48" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B74" s="40" t="inlineStr">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D96" s="33">
+        <f>'HOLERITE SET.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E96" s="48" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C74" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D74" s="44">
-        <f>'HOLERITE SET.26'!D23</f>
-        <v/>
-      </c>
-      <c r="E74" s="48" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="49" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B75" s="49" t="inlineStr">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D97" s="33">
+        <f>'HOLERITE SET.26'!E22</f>
+        <v/>
+      </c>
+      <c r="E97" s="48" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="49" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B98" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C75" s="49" t="inlineStr">
+      <c r="C98" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D75" s="50">
-        <f>'HOLERITE SET.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B76" s="40" t="inlineStr">
+      <c r="D98" s="50">
+        <f>'HOLERITE SET.26'!E23</f>
+        <v/>
+      </c>
+      <c r="E98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B99" s="41" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C76" s="40" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D76" s="44">
-        <f>'HOLERITE SET.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E76" s="48" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B77" s="40" t="inlineStr">
+      <c r="D99" s="33">
+        <f>'HOLERITE SET.26'!E25</f>
+        <v/>
+      </c>
+      <c r="E99" s="48" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B100" s="41" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C77" s="40" t="inlineStr">
+      <c r="C100" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D77" s="44">
-        <f>'HOLERITE SET.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E77" s="48" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B78" s="40" t="inlineStr">
+      <c r="D100" s="33">
+        <f>'HOLERITE SET.26'!E26</f>
+        <v/>
+      </c>
+      <c r="E100" s="48" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B101" s="41" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C78" s="40" t="inlineStr">
+      <c r="C101" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D78" s="44">
-        <f>'HOLERITE SET.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E78" s="48" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B79" s="40" t="inlineStr">
+      <c r="D101" s="33">
+        <f>'HOLERITE SET.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E101" s="48" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B102" s="41" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C79" s="40" t="inlineStr">
+      <c r="C102" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D79" s="44">
-        <f>'HOLERITE SET.26'!D29</f>
-        <v/>
-      </c>
-      <c r="E79" s="48" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B80" s="40" t="inlineStr">
+      <c r="D102" s="33">
+        <f>'HOLERITE SET.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E102" s="48" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B103" s="41" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C80" s="40" t="inlineStr">
+      <c r="C103" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D80" s="44">
-        <f>'HOLERITE SET.26'!D30</f>
-        <v/>
-      </c>
-      <c r="E80" s="48" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B81" s="40" t="inlineStr">
+      <c r="D103" s="33">
+        <f>'HOLERITE SET.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E103" s="48" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B104" s="41" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C81" s="40" t="inlineStr">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D81" s="44">
-        <f>'HOLERITE SET.26'!D31</f>
-        <v/>
-      </c>
-      <c r="E81" s="48" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="40" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B82" s="40" t="inlineStr">
+      <c r="D104" s="33">
+        <f>'HOLERITE SET.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E104" s="48" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="41" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B105" s="41" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C105" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D82" s="44">
-        <f>'HOLERITE SET.26'!D32</f>
-        <v/>
-      </c>
-      <c r="E82" s="48" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="49" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B83" s="49" t="inlineStr">
+      <c r="D105" s="33">
+        <f>'HOLERITE SET.26'!E31</f>
+        <v/>
+      </c>
+      <c r="E105" s="48" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="49" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B106" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C83" s="49" t="inlineStr">
+      <c r="C106" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D83" s="50">
-        <f>'HOLERITE SET.26'!D33</f>
-        <v/>
-      </c>
-      <c r="E83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="51" t="inlineStr">
-        <is>
-          <t>VALDICK</t>
-        </is>
-      </c>
-      <c r="B84" s="52" t="inlineStr">
+      <c r="D106" s="50">
+        <f>'HOLERITE SET.26'!E32</f>
+        <v/>
+      </c>
+      <c r="E106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B107" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C84" s="52" t="inlineStr">
+      <c r="C107" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D84" s="53">
-        <f>'HOLERITE SET.26'!D35</f>
-        <v/>
-      </c>
-      <c r="E84" s="54" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B86" s="40" t="inlineStr">
+      <c r="D107" s="53">
+        <f>'HOLERITE SET.26'!E34</f>
+        <v/>
+      </c>
+      <c r="E107" s="54" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B109" s="41" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C86" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D86" s="44">
-        <f>'HOLERITE SET.26'!E6</f>
-        <v/>
-      </c>
-      <c r="E86" s="48" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B87" s="40" t="inlineStr">
+      <c r="C109" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D109" s="33">
+        <f>'HOLERITE SET.26'!F6</f>
+        <v/>
+      </c>
+      <c r="E109" s="48" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B110" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C87" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D87" s="44">
-        <f>'HOLERITE SET.26'!E7</f>
-        <v/>
-      </c>
-      <c r="E87" s="48" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B88" s="40" t="inlineStr">
+      <c r="C110" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D110" s="33">
+        <f>'HOLERITE SET.26'!F7</f>
+        <v/>
+      </c>
+      <c r="E110" s="48" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B111" s="41" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C88" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D88" s="44">
-        <f>'HOLERITE SET.26'!E8</f>
-        <v/>
-      </c>
-      <c r="E88" s="48" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B89" s="40" t="inlineStr">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D111" s="33">
+        <f>'HOLERITE SET.26'!F8</f>
+        <v/>
+      </c>
+      <c r="E111" s="48" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B112" s="41" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C89" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D89" s="44">
-        <f>'HOLERITE SET.26'!E11</f>
-        <v/>
-      </c>
-      <c r="E89" s="48" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B90" s="40" t="inlineStr">
+      <c r="C112" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D112" s="33">
+        <f>'HOLERITE SET.26'!F11</f>
+        <v/>
+      </c>
+      <c r="E112" s="48" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B113" s="41" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C90" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D90" s="44">
-        <f>'HOLERITE SET.26'!E12</f>
-        <v/>
-      </c>
-      <c r="E90" s="48" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B91" s="40" t="inlineStr">
+      <c r="C113" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D113" s="33">
+        <f>'HOLERITE SET.26'!F12</f>
+        <v/>
+      </c>
+      <c r="E113" s="48" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B114" s="41" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C91" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D91" s="44">
-        <f>'HOLERITE SET.26'!E13</f>
-        <v/>
-      </c>
-      <c r="E91" s="48" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B92" s="40" t="inlineStr">
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D114" s="33">
+        <f>'HOLERITE SET.26'!F13</f>
+        <v/>
+      </c>
+      <c r="E114" s="48" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B115" s="41" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C92" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D92" s="44">
-        <f>'HOLERITE SET.26'!E14</f>
-        <v/>
-      </c>
-      <c r="E92" s="48" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B93" s="40" t="inlineStr">
+      <c r="C115" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D115" s="33">
+        <f>'HOLERITE SET.26'!F14</f>
+        <v/>
+      </c>
+      <c r="E115" s="48" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B116" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D93" s="44">
-        <f>'HOLERITE SET.26'!E15</f>
-        <v/>
-      </c>
-      <c r="E93" s="48" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B94" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C94" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D94" s="44">
-        <f>'HOLERITE SET.26'!E16</f>
-        <v/>
-      </c>
-      <c r="E94" s="48" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B95" s="40" t="inlineStr">
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D116" s="33">
+        <f>'HOLERITE SET.26'!F15</f>
+        <v/>
+      </c>
+      <c r="E116" s="48" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B117" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D95" s="44">
-        <f>'HOLERITE SET.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E95" s="48" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B96" s="40" t="inlineStr">
+      <c r="C117" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D117" s="33">
+        <f>'HOLERITE SET.26'!F16</f>
+        <v/>
+      </c>
+      <c r="E117" s="48" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B118" s="41" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C96" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D96" s="44">
-        <f>'HOLERITE SET.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E96" s="48" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B97" s="40" t="inlineStr">
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D118" s="33">
+        <f>'HOLERITE SET.26'!F17</f>
+        <v/>
+      </c>
+      <c r="E118" s="48" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B119" s="41" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D97" s="44">
-        <f>'HOLERITE SET.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E97" s="48" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B98" s="40" t="inlineStr">
+      <c r="C119" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D119" s="33">
+        <f>'HOLERITE SET.26'!F18</f>
+        <v/>
+      </c>
+      <c r="E119" s="48" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B120" s="41" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C98" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D98" s="44">
-        <f>'HOLERITE SET.26'!E20</f>
-        <v/>
-      </c>
-      <c r="E98" s="48" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B99" s="40" t="inlineStr">
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D120" s="33">
+        <f>'HOLERITE SET.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E120" s="48" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B121" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C99" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D99" s="44">
-        <f>'HOLERITE SET.26'!E21</f>
-        <v/>
-      </c>
-      <c r="E99" s="48" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B100" s="40" t="inlineStr">
+      <c r="C121" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D121" s="33">
+        <f>'HOLERITE SET.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E121" s="48" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B122" s="41" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C100" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D100" s="44">
-        <f>'HOLERITE SET.26'!E22</f>
-        <v/>
-      </c>
-      <c r="E100" s="48" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B101" s="40" t="inlineStr">
+      <c r="C122" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D122" s="33">
+        <f>'HOLERITE SET.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E122" s="48" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B123" s="41" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D101" s="44">
-        <f>'HOLERITE SET.26'!E23</f>
-        <v/>
-      </c>
-      <c r="E101" s="48" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="49" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B102" s="49" t="inlineStr">
+      <c r="C123" s="41" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D123" s="33">
+        <f>'HOLERITE SET.26'!F22</f>
+        <v/>
+      </c>
+      <c r="E123" s="48" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="49" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B124" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C102" s="49" t="inlineStr">
+      <c r="C124" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="50">
-        <f>'HOLERITE SET.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E102" s="18" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B103" s="40" t="inlineStr">
+      <c r="D124" s="50">
+        <f>'HOLERITE SET.26'!F23</f>
+        <v/>
+      </c>
+      <c r="E124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B125" s="41" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C103" s="40" t="inlineStr">
+      <c r="C125" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D103" s="44">
-        <f>'HOLERITE SET.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E103" s="48" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B104" s="40" t="inlineStr">
+      <c r="D125" s="33">
+        <f>'HOLERITE SET.26'!F25</f>
+        <v/>
+      </c>
+      <c r="E125" s="48" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B126" s="41" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C104" s="40" t="inlineStr">
+      <c r="C126" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D104" s="44">
-        <f>'HOLERITE SET.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E104" s="48" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B105" s="40" t="inlineStr">
+      <c r="D126" s="33">
+        <f>'HOLERITE SET.26'!F26</f>
+        <v/>
+      </c>
+      <c r="E126" s="48" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B127" s="41" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C105" s="40" t="inlineStr">
+      <c r="C127" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D105" s="44">
-        <f>'HOLERITE SET.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E105" s="48" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B106" s="40" t="inlineStr">
+      <c r="D127" s="33">
+        <f>'HOLERITE SET.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E127" s="48" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B128" s="41" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C106" s="40" t="inlineStr">
+      <c r="C128" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D106" s="44">
-        <f>'HOLERITE SET.26'!E29</f>
-        <v/>
-      </c>
-      <c r="E106" s="48" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B107" s="40" t="inlineStr">
+      <c r="D128" s="33">
+        <f>'HOLERITE SET.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E128" s="48" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B129" s="41" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C107" s="40" t="inlineStr">
+      <c r="C129" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D107" s="44">
-        <f>'HOLERITE SET.26'!E30</f>
-        <v/>
-      </c>
-      <c r="E107" s="48" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B108" s="40" t="inlineStr">
+      <c r="D129" s="33">
+        <f>'HOLERITE SET.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E129" s="48" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B130" s="41" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C130" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D108" s="44">
-        <f>'HOLERITE SET.26'!E31</f>
-        <v/>
-      </c>
-      <c r="E108" s="48" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="40" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B109" s="40" t="inlineStr">
+      <c r="D130" s="33">
+        <f>'HOLERITE SET.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E130" s="48" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="41" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B131" s="41" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C109" s="40" t="inlineStr">
+      <c r="C131" s="41" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D109" s="44">
-        <f>'HOLERITE SET.26'!E32</f>
-        <v/>
-      </c>
-      <c r="E109" s="48" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="49" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B110" s="49" t="inlineStr">
+      <c r="D131" s="33">
+        <f>'HOLERITE SET.26'!F31</f>
+        <v/>
+      </c>
+      <c r="E131" s="48" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="49" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B132" s="49" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C110" s="49" t="inlineStr">
+      <c r="C132" s="49" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D110" s="50">
-        <f>'HOLERITE SET.26'!E33</f>
-        <v/>
-      </c>
-      <c r="E110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="51" t="inlineStr">
-        <is>
-          <t>INIURLE</t>
-        </is>
-      </c>
-      <c r="B111" s="52" t="inlineStr">
+      <c r="D132" s="50">
+        <f>'HOLERITE SET.26'!F32</f>
+        <v/>
+      </c>
+      <c r="E132" s="18" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="51" t="inlineStr">
+        <is>
+          <t>TAMILES</t>
+        </is>
+      </c>
+      <c r="B133" s="52" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C111" s="52" t="inlineStr">
+      <c r="C133" s="52" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D111" s="53">
-        <f>'HOLERITE SET.26'!E35</f>
-        <v/>
-      </c>
-      <c r="E111" s="54" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B113" s="40" t="inlineStr">
-        <is>
-          <t>SALÁRIO BASE</t>
-        </is>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D113" s="44">
-        <f>'HOLERITE SET.26'!F6</f>
-        <v/>
-      </c>
-      <c r="E113" s="48" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B114" s="40" t="inlineStr">
-        <is>
-          <t>ADICIONAL NOTURNO</t>
-        </is>
-      </c>
-      <c r="C114" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D114" s="44">
-        <f>'HOLERITE SET.26'!F7</f>
-        <v/>
-      </c>
-      <c r="E114" s="48" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B115" s="40" t="inlineStr">
-        <is>
-          <t>HORAS EXTRAS</t>
-        </is>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D115" s="44">
-        <f>'HOLERITE SET.26'!F8</f>
-        <v/>
-      </c>
-      <c r="E115" s="48" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B116" s="40" t="inlineStr">
-        <is>
-          <t>COMISSÃO SOBRE VENDAS</t>
-        </is>
-      </c>
-      <c r="C116" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D116" s="44">
-        <f>'HOLERITE SET.26'!F11</f>
-        <v/>
-      </c>
-      <c r="E116" s="48" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B117" s="40" t="inlineStr">
-        <is>
-          <t>REPOUSO REMUNERADO / DSR</t>
-        </is>
-      </c>
-      <c r="C117" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D117" s="44">
-        <f>'HOLERITE SET.26'!F12</f>
-        <v/>
-      </c>
-      <c r="E117" s="48" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B118" s="40" t="inlineStr">
-        <is>
-          <t>AUXÍLIO GERÊNCIA</t>
-        </is>
-      </c>
-      <c r="C118" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D118" s="44">
-        <f>'HOLERITE SET.26'!F13</f>
-        <v/>
-      </c>
-      <c r="E118" s="48" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B119" s="40" t="inlineStr">
-        <is>
-          <t>ADICIONAL PRÊMIO META CAIXA</t>
-        </is>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D119" s="44">
-        <f>'HOLERITE SET.26'!F14</f>
-        <v/>
-      </c>
-      <c r="E119" s="48" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B120" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 1 — VOLUME</t>
-        </is>
-      </c>
-      <c r="C120" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D120" s="44">
-        <f>'HOLERITE SET.26'!F15</f>
-        <v/>
-      </c>
-      <c r="E120" s="48" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B121" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D121" s="44">
-        <f>'HOLERITE SET.26'!F16</f>
-        <v/>
-      </c>
-      <c r="E121" s="48" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B122" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C122" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D122" s="44">
-        <f>'HOLERITE SET.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E122" s="48" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B123" s="40" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
-        </is>
-      </c>
-      <c r="C123" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D123" s="44">
-        <f>'HOLERITE SET.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E123" s="48" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B124" s="40" t="inlineStr">
-        <is>
-          <t>FÉRIAS</t>
-        </is>
-      </c>
-      <c r="C124" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D124" s="44">
-        <f>'HOLERITE SET.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E124" s="48" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B125" s="40" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="C125" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D125" s="44">
-        <f>'HOLERITE SET.26'!F20</f>
-        <v/>
-      </c>
-      <c r="E125" s="48" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B126" s="40" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="C126" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D126" s="44">
-        <f>'HOLERITE SET.26'!F21</f>
-        <v/>
-      </c>
-      <c r="E126" s="48" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B127" s="40" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="C127" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D127" s="44">
-        <f>'HOLERITE SET.26'!F22</f>
-        <v/>
-      </c>
-      <c r="E127" s="48" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B128" s="40" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="C128" s="40" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D128" s="44">
-        <f>'HOLERITE SET.26'!F23</f>
-        <v/>
-      </c>
-      <c r="E128" s="48" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="49" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B129" s="49" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="C129" s="49" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D129" s="50">
-        <f>'HOLERITE SET.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E129" s="18" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B130" s="40" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="C130" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D130" s="44">
-        <f>'HOLERITE SET.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E130" s="48" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B131" s="40" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="C131" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D131" s="44">
-        <f>'HOLERITE SET.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E131" s="48" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B132" s="40" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="C132" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D132" s="44">
-        <f>'HOLERITE SET.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E132" s="48" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B133" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO FALTAS / ATRASOS</t>
-        </is>
-      </c>
-      <c r="C133" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D133" s="44">
-        <f>'HOLERITE SET.26'!F29</f>
-        <v/>
-      </c>
-      <c r="E133" s="48" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B134" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="C134" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D134" s="44">
-        <f>'HOLERITE SET.26'!F30</f>
-        <v/>
-      </c>
-      <c r="E134" s="48" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B135" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
-        </is>
-      </c>
-      <c r="C135" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D135" s="44">
-        <f>'HOLERITE SET.26'!F31</f>
-        <v/>
-      </c>
-      <c r="E135" s="48" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="40" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B136" s="40" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="C136" s="40" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D136" s="44">
-        <f>'HOLERITE SET.26'!F32</f>
-        <v/>
-      </c>
-      <c r="E136" s="48" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="49" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B137" s="49" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="C137" s="49" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D137" s="50">
-        <f>'HOLERITE SET.26'!F33</f>
-        <v/>
-      </c>
-      <c r="E137" s="18" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="51" t="inlineStr">
-        <is>
-          <t>TAMILES</t>
-        </is>
-      </c>
-      <c r="B138" s="52" t="inlineStr">
-        <is>
-          <t>LÍQUIDO A RECEBER</t>
-        </is>
-      </c>
-      <c r="C138" s="52" t="inlineStr">
-        <is>
-          <t>Líquido</t>
-        </is>
-      </c>
-      <c r="D138" s="53">
-        <f>'HOLERITE SET.26'!F35</f>
-        <v/>
-      </c>
-      <c r="E138" s="54" t="n"/>
+      <c r="D133" s="53">
+        <f>'HOLERITE SET.26'!F34</f>
+        <v/>
+      </c>
+      <c r="E133" s="54" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E138"/>
+  <autoFilter ref="A4:E133"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -6454,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6500,398 +6369,387 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="C6" s="39" t="n"/>
-      <c r="D6" s="39" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$7:$F$7,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$8:$F$8,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="40" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$11:$F$11,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$12:$F$12,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$13:$F$13,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$14:$F$14,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>Prêmio meta 1 — volume</t>
         </is>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$15:$F$15,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Prêmio meta 2 — produtos foco</t>
-        </is>
-      </c>
-      <c r="C15" s="44">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Prêmio meta 3 — pré-vencidos</t>
+        </is>
+      </c>
+      <c r="C15" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$16:$F$16,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="40" t="inlineStr">
-        <is>
-          <t>Prêmio meta 3 — pré-vencidos</t>
-        </is>
-      </c>
-      <c r="C16" s="44">
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Prêmio meta 4 — perfumaria</t>
+        </is>
+      </c>
+      <c r="C16" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$F$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>Prêmio meta 4 — perfumaria</t>
-        </is>
-      </c>
-      <c r="C17" s="44">
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Férias</t>
+        </is>
+      </c>
+      <c r="C17" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$F$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="40" t="inlineStr">
-        <is>
-          <t>Férias</t>
-        </is>
-      </c>
-      <c r="C18" s="44">
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>1/3 constitucional de férias</t>
+        </is>
+      </c>
+      <c r="C18" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$F$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>1/3 constitucional de férias</t>
-        </is>
-      </c>
-      <c r="C19" s="44">
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Incentivo aplicações</t>
+        </is>
+      </c>
+      <c r="C19" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$F$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="40" t="inlineStr">
-        <is>
-          <t>Incentivo aplicações</t>
-        </is>
-      </c>
-      <c r="C20" s="44">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Incentivo vitaminas</t>
+        </is>
+      </c>
+      <c r="C20" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$F$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>Incentivo vitaminas</t>
-        </is>
-      </c>
-      <c r="C21" s="44">
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Outros incentivos</t>
+        </is>
+      </c>
+      <c r="C21" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$F$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t>Outros incentivos</t>
-        </is>
-      </c>
-      <c r="C22" s="44">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C22" s="50">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$23:$F$23,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="C23" s="50">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$F$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS</t>
         </is>
       </c>
-      <c r="C24" s="39" t="n"/>
-      <c r="D24" s="39" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>Adiantamento salarial / vales</t>
+        </is>
+      </c>
+      <c r="C24" s="33">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$25:$F$25,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>Adiantamento salarial / vales</t>
-        </is>
-      </c>
-      <c r="C25" s="44">
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>Adiantamento de incentivos e aplicações</t>
+        </is>
+      </c>
+      <c r="C25" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$F$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="40" t="inlineStr">
-        <is>
-          <t>Adiantamento de incentivos e aplicações</t>
-        </is>
-      </c>
-      <c r="C26" s="44">
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>Convênio</t>
+        </is>
+      </c>
+      <c r="C26" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$F$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>Convênio</t>
-        </is>
-      </c>
-      <c r="C27" s="44">
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>Faltas / atrasos</t>
+        </is>
+      </c>
+      <c r="C27" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$F$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>Faltas / atrasos</t>
-        </is>
-      </c>
-      <c r="C28" s="44">
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>Vale transporte 6%</t>
+        </is>
+      </c>
+      <c r="C28" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$F$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="40" t="inlineStr">
-        <is>
-          <t>Vale transporte 6%</t>
-        </is>
-      </c>
-      <c r="C29" s="44">
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="C29" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$F$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="40" t="inlineStr">
-        <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="C30" s="44">
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>IRRF</t>
+        </is>
+      </c>
+      <c r="C30" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$F$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="40" t="inlineStr">
-        <is>
-          <t>IRRF</t>
-        </is>
-      </c>
-      <c r="C31" s="44">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C31" s="50">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$32:$F$32,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="C32" s="50">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$F$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="39" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="57" t="inlineStr">
+      <c r="C32" s="40" t="n"/>
+      <c r="D32" s="40" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="57" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/10/2026</t>
         </is>
       </c>
-      <c r="C34" s="58">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$35:$F$35,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
-        <v/>
+      <c r="C33" s="58">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$34:$F$34,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Vendas do colaborador no mês (InovaFarma):</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Vendas do colaborador no mês (InovaFarma):</t>
-        </is>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Venda bruta</t>
+        </is>
+      </c>
+      <c r="C36" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>Venda bruta</t>
-        </is>
-      </c>
-      <c r="C37" s="44">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Descontos concedidos</t>
+        </is>
+      </c>
+      <c r="C37" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>Descontos concedidos</t>
-        </is>
-      </c>
-      <c r="C38" s="44">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Venda líquida</t>
+        </is>
+      </c>
+      <c r="C38" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="40" t="inlineStr">
-        <is>
-          <t>Venda líquida</t>
-        </is>
-      </c>
-      <c r="C39" s="44">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>Comissão apurada</t>
+        </is>
+      </c>
+      <c r="C39" s="33">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>Comissão apurada</t>
-        </is>
-      </c>
-      <c r="C40" s="44">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="40" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C41" s="44">
+      <c r="C40" s="33">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$9,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$9,0)),0)</f>
         <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="47" t="inlineStr">
+        <is>
+          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
+          <t>Nesta loja a comissão paga é o DOBRO da apurada — por isso os dois valores são diferentes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>Nesta loja a comissão paga é o DOBRO da apurada — por isso os dois valores são diferentes.</t>
+          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="47" t="inlineStr">
-        <is>
-          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="47" t="inlineStr">
         <is>
           <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
         </is>
@@ -6999,7 +6857,7 @@
           <t>VALDICK</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -7012,7 +6870,7 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A5,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7028,7 +6886,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
         </is>
@@ -7040,7 +6898,7 @@
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Atestado médico (abonado)</t>
         </is>
@@ -7053,7 +6911,7 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7069,7 +6927,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="43" t="inlineStr">
+      <c r="I6" s="44" t="inlineStr">
         <is>
           <t>Atestado médico de 02 a 08/09/2026, entregue em 02/09. Até 15 dias é abonado pela empresa: falta justificada, SEM desconto de salário nem de DSR. Anexar o atestado à pasta da funcionária.</t>
         </is>
@@ -7080,7 +6938,7 @@
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
-      <c r="E7" s="44">
+      <c r="E7" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A7,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7097,7 +6955,7 @@
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
-      <c r="E8" s="44">
+      <c r="E8" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A8,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7114,7 +6972,7 @@
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
-      <c r="E9" s="44">
+      <c r="E9" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A9,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7131,7 +6989,7 @@
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
       <c r="D10" s="27" t="n"/>
-      <c r="E10" s="44">
+      <c r="E10" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A10,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7148,7 +7006,7 @@
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="27" t="n"/>
-      <c r="E11" s="44">
+      <c r="E11" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A11,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7165,7 +7023,7 @@
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="27" t="n"/>
       <c r="D12" s="27" t="n"/>
-      <c r="E12" s="44">
+      <c r="E12" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A12,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7182,7 +7040,7 @@
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="27" t="n"/>
       <c r="D13" s="27" t="n"/>
-      <c r="E13" s="44">
+      <c r="E13" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A13,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
@@ -7199,7 +7057,7 @@
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="27" t="n"/>
       <c r="D14" s="27" t="n"/>
-      <c r="E14" s="44">
+      <c r="E14" s="33">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$F$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
